--- a/HSE Dashboard Rev 0(3).xlsx
+++ b/HSE Dashboard Rev 0(3).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://databasehub-my.sharepoint.com/personal/hse_databasehub_onmicrosoft_com/Documents/POM HSE DOCUMENTATION/DASHBOARD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="11_50060B46BD35296F53D3E59C33CD99FCCDC13A9C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41D0CDE2-DB26-417E-83E4-13A47A7A94D0}"/>
+  <xr:revisionPtr revIDLastSave="123" documentId="11_50060B46BD35296F53D3E59C33CD99FCCDC13A9C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D182131-B968-4B26-AF5D-ED659C8F05EB}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="9" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="105" yWindow="1980" windowWidth="28800" windowHeight="15345" firstSheet="9" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POM_Office" sheetId="1" r:id="rId1"/>
@@ -1633,7 +1633,7 @@
     <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="167" formatCode="dd\-mmm\-yyyy;@"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1691,6 +1691,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1925,7 +1931,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2063,25 +2069,22 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2108,12 +2111,28 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial Narrow"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
         <family val="2"/>
       </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2123,12 +2142,28 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial Narrow"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
         <family val="2"/>
       </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2138,40 +2173,21 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial Narrow"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial Narrow"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
         <family val="2"/>
       </font>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border>
         <left style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
         </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
@@ -2184,38 +2200,21 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial Narrow"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial Narrow"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
         <family val="2"/>
       </font>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border>
         <left style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </left>
         <right/>
-        <top style="hair">
-          <color indexed="64"/>
+        <top style="thin">
+          <color rgb="FF000000"/>
         </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
@@ -2228,25 +2227,86 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial Narrow"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Arial"/>
         <family val="2"/>
       </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <numFmt numFmtId="167" formatCode="dd\-mmm\-yyyy;@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <border>
         <left style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
         </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
@@ -2259,23 +2319,28 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
+        <sz val="9"/>
         <color theme="1"/>
-        <name val="Arial Narrow"/>
+        <name val="Arial"/>
         <family val="2"/>
       </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <border outline="0">
         <left style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </left>
         <right/>
-        <top style="hair">
-          <color indexed="64"/>
+        <top style="thin">
+          <color rgb="FF000000"/>
         </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -2286,25 +2351,30 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial Narrow"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
         <family val="2"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border outline="0">
+      <border>
         <left style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
         </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2315,26 +2385,27 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial Narrow"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border outline="0">
         <left style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
         </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -2345,26 +2416,27 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial Narrow"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="164" formatCode="dddd"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border outline="0">
         <left style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
         </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -2375,24 +2447,58 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
+        <sz val="9"/>
         <color theme="1"/>
-        <name val="Arial Narrow"/>
+        <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <border outline="0">
         <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
         </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -2406,9 +2512,6 @@
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
-        <bottom style="hair">
-          <color rgb="FF000000"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -2419,19 +2522,18 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial Narrow"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Arial"/>
         <family val="2"/>
       </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </dxf>
     <dxf>
       <font>
@@ -2442,24 +2544,18 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial Narrow"/>
+        <sz val="9"/>
+        <color theme="0"/>
+        <name val="Arial"/>
         <family val="2"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border outline="0">
         <left style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </left>
         <right style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </right>
         <top/>
         <bottom/>
@@ -7298,28 +7394,12 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial Narrow"/>
         <family val="2"/>
       </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -7329,28 +7409,12 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial Narrow"/>
         <family val="2"/>
       </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom/>
-      </border>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -7360,21 +7424,40 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial Narrow"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial Narrow"/>
         <family val="2"/>
       </font>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border>
         <left style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
         <vertical/>
         <horizontal/>
       </border>
@@ -7387,21 +7470,38 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial Narrow"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial Narrow"/>
         <family val="2"/>
       </font>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border>
         <left style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </left>
         <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
+        <top style="hair">
+          <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
         <vertical/>
         <horizontal/>
       </border>
@@ -7414,86 +7514,25 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Arial"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial Narrow"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="167" formatCode="dd\-mmm\-yyyy;@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border>
         <left style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
         <vertical/>
         <horizontal/>
       </border>
@@ -7506,28 +7545,23 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Arial"/>
+        <name val="Arial Narrow"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border outline="0">
         <left style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </left>
         <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
+        <top style="hair">
+          <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -7538,30 +7572,25 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial Narrow"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
+      <border outline="0">
         <left style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
         </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -7572,27 +7601,26 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial Narrow"/>
         <family val="2"/>
       </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border outline="0">
         <left style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -7603,27 +7631,26 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial Narrow"/>
         <family val="2"/>
       </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="164" formatCode="dddd"/>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border outline="0">
         <left style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -7634,58 +7661,24 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Arial"/>
+        <name val="Arial Narrow"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border outline="0">
         <left/>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -7699,6 +7692,9 @@
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
+        <bottom style="hair">
+          <color rgb="FF000000"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -7709,18 +7705,19 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Arial"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial Narrow"/>
         <family val="2"/>
       </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -7731,18 +7728,24 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="0"/>
-        <name val="Arial"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial Narrow"/>
         <family val="2"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border outline="0">
         <left style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </right>
         <top/>
         <bottom/>
@@ -7934,8 +7937,8 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{00000000-000C-0000-FFFF-FFFF0F000000}" name="Leading" displayName="Leading" ref="A5:O171" totalsRowShown="0" headerRowDxfId="35" dataDxfId="33" headerRowBorderDxfId="34" tableBorderDxfId="32">
-  <autoFilter ref="A5:O171" xr:uid="{00000000-0009-0000-0100-000010000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{00000000-000C-0000-FFFF-FFFF0F000000}" name="Leading" displayName="Leading" ref="A5:O178" totalsRowShown="0" headerRowDxfId="35" dataDxfId="33" headerRowBorderDxfId="34" tableBorderDxfId="32">
+  <autoFilter ref="A5:O178" xr:uid="{00000000-0009-0000-0100-000010000000}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0F00-000001000000}" name="DATE" dataDxfId="31"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0F00-000002000000}" name="DAY" dataDxfId="30">
@@ -7967,18 +7970,18 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{00000000-000C-0000-FFFF-FFFF10000000}" name="Table3" displayName="Table3" ref="A1:M170" totalsRowShown="0" headerRowDxfId="223" dataDxfId="222" tableBorderDxfId="221">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{00000000-000C-0000-FFFF-FFFF10000000}" name="Table3" displayName="Table3" ref="A1:M170" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15" tableBorderDxfId="14">
   <autoFilter ref="A1:M170" xr:uid="{00000000-0009-0000-0100-000011000000}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1000-000001000000}" name="No" dataDxfId="220"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1000-000002000000}" name="BSC No" dataDxfId="219"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1000-000003000000}" name="BSC Type" dataDxfId="218"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1000-000004000000}" name="Hazard Type RAW" dataDxfId="217"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-1000-00000A000000}" name="Hazard Type" dataDxfId="216">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1000-000001000000}" name="No" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1000-000002000000}" name="BSC No" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1000-000003000000}" name="BSC Type" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1000-000004000000}" name="Hazard Type RAW" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-1000-00000A000000}" name="Hazard Type" dataDxfId="9">
       <calculatedColumnFormula>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1000-000005000000}" name="Date Reported" dataDxfId="215"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-1000-00000B000000}" name="Week" dataDxfId="214" dataCellStyle="Normal 2">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1000-000005000000}" name="Date Reported" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-1000-00000B000000}" name="Week" dataDxfId="7" dataCellStyle="Normal 2">
       <calculatedColumnFormula>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -7986,26 +7989,26 @@
 "W"&amp;TEXT(_xlpm.W,"00")&amp;" ("&amp;TEXT(_xlpm.S,"d/m")&amp;" - "&amp;TEXT(_xlpm.E,"d/m")&amp;")"
 ))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1000-000006000000}" name="Date Observed" dataDxfId="213"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-1000-000007000000}" name="Observed By" dataDxfId="212"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-1000-00000C000000}" name="Company" dataDxfId="211" dataCellStyle="Normal 2"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-1000-00000D000000}" name="Position" dataDxfId="210" dataCellStyle="Normal 2"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-1000-000008000000}" name="What and where hazard/act observed and_x000a_discussed with worker/supervisor/manager?" dataDxfId="209"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-1000-000009000000}" name="Status" dataDxfId="208"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1000-000006000000}" name="Date Observed" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-1000-000007000000}" name="Observed By" dataDxfId="5"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-1000-00000C000000}" name="Company" dataDxfId="4" dataCellStyle="Normal 2"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-1000-00000D000000}" name="Position" dataDxfId="3" dataCellStyle="Normal 2"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-1000-000008000000}" name="What and where hazard/act observed and_x000a_discussed with worker/supervisor/manager?" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-1000-000009000000}" name="Status" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{00000000-000C-0000-FFFF-FFFF11000000}" name="Leading20" displayName="Leading20" ref="A5:L176" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{00000000-000C-0000-FFFF-FFFF11000000}" name="Leading20" displayName="Leading20" ref="A5:L176" totalsRowShown="0" headerRowDxfId="223" dataDxfId="221" headerRowBorderDxfId="222" tableBorderDxfId="220">
   <autoFilter ref="A5:L176" xr:uid="{00000000-0009-0000-0100-000012000000}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1100-000001000000}" name="DATE" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1100-000002000000}" name="DAY" dataDxfId="11">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1100-000001000000}" name="DATE" dataDxfId="219"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1100-000002000000}" name="DAY" dataDxfId="218">
       <calculatedColumnFormula>A6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1100-000003000000}" name="WEEK" dataDxfId="10">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1100-000003000000}" name="WEEK" dataDxfId="217">
       <calculatedColumnFormula>IF(Leading20[[#This Row],[DATE]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Leading20[[#This Row],[DATE]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -8013,15 +8016,15 @@
 "W"&amp;TEXT(_xlpm.W,"00")&amp;" ("&amp;TEXT(_xlpm.S,"d/m")&amp;" - "&amp;TEXT(_xlpm.E,"d/m")&amp;")"
 ))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1100-000006000000}" name="SIC" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-1100-000007000000}" name="PTW NOVADE" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1100-000004000000}" name="EMERGENCY RESPONSE" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1100-000005000000}" name="FIRE WATCH" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-1100-000008000000}" name="CHEMICAL HANDLING" dataDxfId="5"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-1100-00000F000000}" name="WASTE MANAGEMENT" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-1100-000009000000}" name="ELECTRICAL SAFETY" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-1100-00000A000000}" name="PPE AWARENESS" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-1100-00000B000000}" name="HAND TOOLS &amp; POWER TOOLS SAFETY" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1100-000006000000}" name="SIC" dataDxfId="216"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-1100-000007000000}" name="PTW NOVADE" dataDxfId="215"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1100-000004000000}" name="EMERGENCY RESPONSE" dataDxfId="214"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1100-000005000000}" name="FIRE WATCH" dataDxfId="213"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-1100-000008000000}" name="CHEMICAL HANDLING" dataDxfId="212"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-1100-00000F000000}" name="WASTE MANAGEMENT" dataDxfId="211"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-1100-000009000000}" name="ELECTRICAL SAFETY" dataDxfId="210"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-1100-00000A000000}" name="PPE AWARENESS" dataDxfId="209"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-1100-00000B000000}" name="HAND TOOLS &amp; POWER TOOLS SAFETY" dataDxfId="208"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -31895,7 +31898,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A5:O171"/>
+  <dimension ref="A5:O178"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" style="13" customWidth="1"/>
@@ -40914,6 +40917,384 @@
         <v>2</v>
       </c>
       <c r="O171" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A172" s="33">
+        <v>46291</v>
+      </c>
+      <c r="B172" s="34">
+        <f t="shared" ref="B172:B176" si="6">A172</f>
+        <v>46291</v>
+      </c>
+      <c r="C172" s="50" t="str">
+        <f>IF(Leading[[#This Row],[DATE]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
+_xlpm.W,INT((Leading[[#This Row],[DATE]]-DATE(2026,4,11))/7)+1,
+_xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
+_xlpm.E,_xlpm.S+6,
+"W"&amp;TEXT(_xlpm.W,"00")&amp;" ("&amp;TEXT(_xlpm.S,"d/m")&amp;" - "&amp;TEXT(_xlpm.E,"d/m")&amp;")"
+))</f>
+        <v>W25 (26/9 - 2/10)</v>
+      </c>
+      <c r="D172" s="35">
+        <v>0</v>
+      </c>
+      <c r="E172" s="35">
+        <v>1</v>
+      </c>
+      <c r="F172" s="35">
+        <v>0</v>
+      </c>
+      <c r="G172" s="35">
+        <v>0</v>
+      </c>
+      <c r="H172" s="35">
+        <v>0</v>
+      </c>
+      <c r="I172" s="35">
+        <v>0</v>
+      </c>
+      <c r="J172" s="35">
+        <v>0</v>
+      </c>
+      <c r="K172" s="35">
+        <v>0</v>
+      </c>
+      <c r="L172" s="35">
+        <v>0</v>
+      </c>
+      <c r="M172" s="35">
+        <v>0</v>
+      </c>
+      <c r="N172" s="35">
+        <v>0</v>
+      </c>
+      <c r="O172" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A173" s="33">
+        <v>46292</v>
+      </c>
+      <c r="B173" s="34">
+        <f t="shared" si="6"/>
+        <v>46292</v>
+      </c>
+      <c r="C173" s="50" t="str">
+        <f>IF(Leading[[#This Row],[DATE]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
+_xlpm.W,INT((Leading[[#This Row],[DATE]]-DATE(2026,4,11))/7)+1,
+_xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
+_xlpm.E,_xlpm.S+6,
+"W"&amp;TEXT(_xlpm.W,"00")&amp;" ("&amp;TEXT(_xlpm.S,"d/m")&amp;" - "&amp;TEXT(_xlpm.E,"d/m")&amp;")"
+))</f>
+        <v>W25 (26/9 - 2/10)</v>
+      </c>
+      <c r="D173" s="35">
+        <v>0</v>
+      </c>
+      <c r="E173" s="35">
+        <v>1</v>
+      </c>
+      <c r="F173" s="35">
+        <v>0</v>
+      </c>
+      <c r="G173" s="35">
+        <v>0</v>
+      </c>
+      <c r="H173" s="35">
+        <v>0</v>
+      </c>
+      <c r="I173" s="35">
+        <v>0</v>
+      </c>
+      <c r="J173" s="35">
+        <v>0</v>
+      </c>
+      <c r="K173" s="35">
+        <v>0</v>
+      </c>
+      <c r="L173" s="35">
+        <v>0</v>
+      </c>
+      <c r="M173" s="35">
+        <v>0</v>
+      </c>
+      <c r="N173" s="35">
+        <v>0</v>
+      </c>
+      <c r="O173" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A174" s="33">
+        <v>46293</v>
+      </c>
+      <c r="B174" s="34">
+        <f t="shared" si="6"/>
+        <v>46293</v>
+      </c>
+      <c r="C174" s="50" t="str">
+        <f>IF(Leading[[#This Row],[DATE]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
+_xlpm.W,INT((Leading[[#This Row],[DATE]]-DATE(2026,4,11))/7)+1,
+_xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
+_xlpm.E,_xlpm.S+6,
+"W"&amp;TEXT(_xlpm.W,"00")&amp;" ("&amp;TEXT(_xlpm.S,"d/m")&amp;" - "&amp;TEXT(_xlpm.E,"d/m")&amp;")"
+))</f>
+        <v>W25 (26/9 - 2/10)</v>
+      </c>
+      <c r="D174" s="35">
+        <v>0</v>
+      </c>
+      <c r="E174" s="35">
+        <v>1</v>
+      </c>
+      <c r="F174" s="35">
+        <v>0</v>
+      </c>
+      <c r="G174" s="35">
+        <v>0</v>
+      </c>
+      <c r="H174" s="35">
+        <v>0</v>
+      </c>
+      <c r="I174" s="35">
+        <v>0</v>
+      </c>
+      <c r="J174" s="35">
+        <v>0</v>
+      </c>
+      <c r="K174" s="35">
+        <v>0</v>
+      </c>
+      <c r="L174" s="35">
+        <v>0</v>
+      </c>
+      <c r="M174" s="35">
+        <v>0</v>
+      </c>
+      <c r="N174" s="35">
+        <v>0</v>
+      </c>
+      <c r="O174" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A175" s="33">
+        <v>46294</v>
+      </c>
+      <c r="B175" s="34">
+        <f t="shared" si="6"/>
+        <v>46294</v>
+      </c>
+      <c r="C175" s="50" t="str">
+        <f>IF(Leading[[#This Row],[DATE]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
+_xlpm.W,INT((Leading[[#This Row],[DATE]]-DATE(2026,4,11))/7)+1,
+_xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
+_xlpm.E,_xlpm.S+6,
+"W"&amp;TEXT(_xlpm.W,"00")&amp;" ("&amp;TEXT(_xlpm.S,"d/m")&amp;" - "&amp;TEXT(_xlpm.E,"d/m")&amp;")"
+))</f>
+        <v>W25 (26/9 - 2/10)</v>
+      </c>
+      <c r="D175" s="35">
+        <v>0</v>
+      </c>
+      <c r="E175" s="35">
+        <v>1</v>
+      </c>
+      <c r="F175" s="35">
+        <v>0</v>
+      </c>
+      <c r="G175" s="35">
+        <v>0</v>
+      </c>
+      <c r="H175" s="35">
+        <v>0</v>
+      </c>
+      <c r="I175" s="35">
+        <v>0</v>
+      </c>
+      <c r="J175" s="35">
+        <v>0</v>
+      </c>
+      <c r="K175" s="35">
+        <v>0</v>
+      </c>
+      <c r="L175" s="35">
+        <v>3</v>
+      </c>
+      <c r="M175" s="35">
+        <v>0</v>
+      </c>
+      <c r="N175" s="35">
+        <v>0</v>
+      </c>
+      <c r="O175" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A176" s="33">
+        <v>46295</v>
+      </c>
+      <c r="B176" s="34">
+        <f t="shared" si="6"/>
+        <v>46295</v>
+      </c>
+      <c r="C176" s="50" t="str">
+        <f>IF(Leading[[#This Row],[DATE]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
+_xlpm.W,INT((Leading[[#This Row],[DATE]]-DATE(2026,4,11))/7)+1,
+_xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
+_xlpm.E,_xlpm.S+6,
+"W"&amp;TEXT(_xlpm.W,"00")&amp;" ("&amp;TEXT(_xlpm.S,"d/m")&amp;" - "&amp;TEXT(_xlpm.E,"d/m")&amp;")"
+))</f>
+        <v>W25 (26/9 - 2/10)</v>
+      </c>
+      <c r="D176" s="35">
+        <v>1</v>
+      </c>
+      <c r="E176" s="35">
+        <v>1</v>
+      </c>
+      <c r="F176" s="35">
+        <v>0</v>
+      </c>
+      <c r="G176" s="52">
+        <v>1</v>
+      </c>
+      <c r="H176" s="35">
+        <v>0</v>
+      </c>
+      <c r="I176" s="35">
+        <v>0</v>
+      </c>
+      <c r="J176" s="35">
+        <v>1</v>
+      </c>
+      <c r="K176" s="35">
+        <v>0</v>
+      </c>
+      <c r="L176" s="35">
+        <v>0</v>
+      </c>
+      <c r="M176" s="35">
+        <v>0</v>
+      </c>
+      <c r="N176" s="35">
+        <v>0</v>
+      </c>
+      <c r="O176" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A177" s="33">
+        <v>46296</v>
+      </c>
+      <c r="B177" s="34">
+        <f t="shared" ref="B177:B178" si="7">A177</f>
+        <v>46296</v>
+      </c>
+      <c r="C177" s="50" t="str">
+        <f>IF(Leading[[#This Row],[DATE]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
+_xlpm.W,INT((Leading[[#This Row],[DATE]]-DATE(2026,4,11))/7)+1,
+_xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
+_xlpm.E,_xlpm.S+6,
+"W"&amp;TEXT(_xlpm.W,"00")&amp;" ("&amp;TEXT(_xlpm.S,"d/m")&amp;" - "&amp;TEXT(_xlpm.E,"d/m")&amp;")"
+))</f>
+        <v>W25 (26/9 - 2/10)</v>
+      </c>
+      <c r="D177" s="35">
+        <v>1</v>
+      </c>
+      <c r="E177" s="35">
+        <v>1</v>
+      </c>
+      <c r="F177" s="51">
+        <v>1</v>
+      </c>
+      <c r="G177" s="52">
+        <v>0</v>
+      </c>
+      <c r="H177" s="35">
+        <v>0</v>
+      </c>
+      <c r="I177" s="35">
+        <v>0</v>
+      </c>
+      <c r="J177" s="35">
+        <v>1</v>
+      </c>
+      <c r="K177" s="35">
+        <v>0</v>
+      </c>
+      <c r="L177" s="35">
+        <v>5</v>
+      </c>
+      <c r="M177" s="35">
+        <v>0</v>
+      </c>
+      <c r="N177" s="35">
+        <v>0</v>
+      </c>
+      <c r="O177" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A178" s="33">
+        <v>46297</v>
+      </c>
+      <c r="B178" s="34">
+        <f t="shared" si="7"/>
+        <v>46297</v>
+      </c>
+      <c r="C178" s="50" t="str">
+        <f>IF(Leading[[#This Row],[DATE]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
+_xlpm.W,INT((Leading[[#This Row],[DATE]]-DATE(2026,4,11))/7)+1,
+_xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
+_xlpm.E,_xlpm.S+6,
+"W"&amp;TEXT(_xlpm.W,"00")&amp;" ("&amp;TEXT(_xlpm.S,"d/m")&amp;" - "&amp;TEXT(_xlpm.E,"d/m")&amp;")"
+))</f>
+        <v>W25 (26/9 - 2/10)</v>
+      </c>
+      <c r="D178" s="35">
+        <v>1</v>
+      </c>
+      <c r="E178" s="35">
+        <v>1</v>
+      </c>
+      <c r="F178" s="51">
+        <v>0</v>
+      </c>
+      <c r="G178" s="52">
+        <v>0</v>
+      </c>
+      <c r="H178" s="35">
+        <v>0</v>
+      </c>
+      <c r="I178" s="35">
+        <v>0</v>
+      </c>
+      <c r="J178" s="35">
+        <v>1</v>
+      </c>
+      <c r="K178" s="35">
+        <v>1</v>
+      </c>
+      <c r="L178" s="35">
+        <v>19</v>
+      </c>
+      <c r="M178" s="35">
+        <v>0</v>
+      </c>
+      <c r="N178" s="35">
+        <v>0</v>
+      </c>
+      <c r="O178" s="35">
         <v>0</v>
       </c>
     </row>
@@ -47752,26 +48133,26 @@
       </c>
     </row>
     <row r="143" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="47">
+      <c r="A143" s="43">
         <v>142</v>
       </c>
-      <c r="B143" s="47" t="s">
+      <c r="B143" s="43" t="s">
         <v>411</v>
       </c>
-      <c r="C143" s="48" t="s">
+      <c r="C143" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="D143" s="48" t="s">
+      <c r="D143" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="E143" s="48" t="str">
+      <c r="E143" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
         <v>Good Catch</v>
       </c>
-      <c r="F143" s="49">
+      <c r="F143" s="45">
         <v>46290</v>
       </c>
-      <c r="G143" s="49" t="str">
+      <c r="G143" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -47780,46 +48161,46 @@
 ))</f>
         <v>W24 (19/9 - 25/9)</v>
       </c>
-      <c r="H143" s="49">
+      <c r="H143" s="45">
         <v>46290</v>
       </c>
-      <c r="I143" s="48" t="s">
+      <c r="I143" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="J143" s="48" t="s">
+      <c r="J143" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="K143" s="48" t="s">
+      <c r="K143" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="L143" s="50" t="s">
+      <c r="L143" s="46" t="s">
         <v>412</v>
       </c>
-      <c r="M143" s="48" t="s">
+      <c r="M143" s="44" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="144" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="47">
+      <c r="A144" s="43">
         <v>143</v>
       </c>
-      <c r="B144" s="47" t="s">
+      <c r="B144" s="43" t="s">
         <v>428</v>
       </c>
-      <c r="C144" s="48" t="s">
+      <c r="C144" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="D144" s="48" t="s">
+      <c r="D144" s="44" t="s">
         <v>429</v>
       </c>
-      <c r="E144" s="48" t="str">
+      <c r="E144" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
         <v>Inadequate or Improper Protective</v>
       </c>
-      <c r="F144" s="49">
+      <c r="F144" s="45">
         <v>46294</v>
       </c>
-      <c r="G144" s="49" t="str">
+      <c r="G144" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -47828,46 +48209,46 @@
 ))</f>
         <v>W25 (26/9 - 2/10)</v>
       </c>
-      <c r="H144" s="49">
+      <c r="H144" s="45">
         <v>46294</v>
       </c>
-      <c r="I144" s="51" t="s">
+      <c r="I144" s="47" t="s">
         <v>111</v>
       </c>
-      <c r="J144" s="48" t="s">
+      <c r="J144" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="K144" s="48" t="s">
+      <c r="K144" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="L144" s="52" t="s">
+      <c r="L144" s="48" t="s">
         <v>430</v>
       </c>
-      <c r="M144" s="53" t="s">
+      <c r="M144" s="49" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="145" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="47">
+      <c r="A145" s="43">
         <v>144</v>
       </c>
-      <c r="B145" s="47" t="s">
+      <c r="B145" s="43" t="s">
         <v>431</v>
       </c>
-      <c r="C145" s="48" t="s">
+      <c r="C145" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="D145" s="48" t="s">
+      <c r="D145" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="E145" s="48" t="str">
+      <c r="E145" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
         <v>Good Catch</v>
       </c>
-      <c r="F145" s="49">
+      <c r="F145" s="45">
         <v>46294</v>
       </c>
-      <c r="G145" s="49" t="str">
+      <c r="G145" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -47876,46 +48257,46 @@
 ))</f>
         <v>W25 (26/9 - 2/10)</v>
       </c>
-      <c r="H145" s="49">
+      <c r="H145" s="45">
         <v>46294</v>
       </c>
-      <c r="I145" s="51" t="s">
+      <c r="I145" s="47" t="s">
         <v>111</v>
       </c>
-      <c r="J145" s="48" t="s">
+      <c r="J145" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="K145" s="48" t="s">
+      <c r="K145" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="L145" s="52" t="s">
+      <c r="L145" s="48" t="s">
         <v>432</v>
       </c>
-      <c r="M145" s="53" t="s">
+      <c r="M145" s="49" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="146" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="47">
+      <c r="A146" s="43">
         <v>145</v>
       </c>
-      <c r="B146" s="47" t="s">
+      <c r="B146" s="43" t="s">
         <v>433</v>
       </c>
-      <c r="C146" s="48" t="s">
+      <c r="C146" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="D146" s="48" t="s">
+      <c r="D146" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="E146" s="48" t="str">
+      <c r="E146" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
         <v>Others - Hazardous Environmental Condition</v>
       </c>
-      <c r="F146" s="49">
+      <c r="F146" s="45">
         <v>46294</v>
       </c>
-      <c r="G146" s="49" t="str">
+      <c r="G146" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -47924,46 +48305,46 @@
 ))</f>
         <v>W25 (26/9 - 2/10)</v>
       </c>
-      <c r="H146" s="49">
+      <c r="H146" s="45">
         <v>46294</v>
       </c>
-      <c r="I146" s="51" t="s">
+      <c r="I146" s="47" t="s">
         <v>81</v>
       </c>
-      <c r="J146" s="48" t="s">
+      <c r="J146" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="K146" s="48" t="s">
+      <c r="K146" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="L146" s="52" t="s">
+      <c r="L146" s="48" t="s">
         <v>434</v>
       </c>
-      <c r="M146" s="53" t="s">
+      <c r="M146" s="49" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="147" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="47">
+      <c r="A147" s="43">
         <v>146</v>
       </c>
-      <c r="B147" s="47" t="s">
+      <c r="B147" s="43" t="s">
         <v>435</v>
       </c>
-      <c r="C147" s="48" t="s">
+      <c r="C147" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="D147" s="48" t="s">
+      <c r="D147" s="44" t="s">
         <v>429</v>
       </c>
-      <c r="E147" s="48" t="str">
+      <c r="E147" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
         <v>Inadequate or Improper Protective</v>
       </c>
-      <c r="F147" s="49">
+      <c r="F147" s="45">
         <v>46296</v>
       </c>
-      <c r="G147" s="49" t="str">
+      <c r="G147" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -47972,46 +48353,46 @@
 ))</f>
         <v>W25 (26/9 - 2/10)</v>
       </c>
-      <c r="H147" s="49">
+      <c r="H147" s="45">
         <v>46296</v>
       </c>
-      <c r="I147" s="51" t="s">
+      <c r="I147" s="47" t="s">
         <v>436</v>
       </c>
-      <c r="J147" s="48" t="s">
+      <c r="J147" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="K147" s="48" t="s">
+      <c r="K147" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="L147" s="52" t="s">
+      <c r="L147" s="48" t="s">
         <v>437</v>
       </c>
-      <c r="M147" s="53" t="s">
+      <c r="M147" s="49" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="148" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="47">
+      <c r="A148" s="43">
         <v>147</v>
       </c>
-      <c r="B148" s="47" t="s">
+      <c r="B148" s="43" t="s">
         <v>438</v>
       </c>
-      <c r="C148" s="48" t="s">
+      <c r="C148" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="D148" s="48" t="s">
+      <c r="D148" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="E148" s="48" t="str">
+      <c r="E148" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
         <v>Inadequate Warning System</v>
       </c>
-      <c r="F148" s="49">
+      <c r="F148" s="45">
         <v>46296</v>
       </c>
-      <c r="G148" s="49" t="str">
+      <c r="G148" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -48020,46 +48401,46 @@
 ))</f>
         <v>W25 (26/9 - 2/10)</v>
       </c>
-      <c r="H148" s="49">
+      <c r="H148" s="45">
         <v>46296</v>
       </c>
-      <c r="I148" s="51" t="s">
+      <c r="I148" s="47" t="s">
         <v>199</v>
       </c>
-      <c r="J148" s="48" t="s">
+      <c r="J148" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="K148" s="48" t="s">
+      <c r="K148" s="44" t="s">
         <v>193</v>
       </c>
-      <c r="L148" s="52" t="s">
+      <c r="L148" s="48" t="s">
         <v>439</v>
       </c>
-      <c r="M148" s="53" t="s">
+      <c r="M148" s="49" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="149" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="47">
+      <c r="A149" s="43">
         <v>148</v>
       </c>
-      <c r="B149" s="47" t="s">
+      <c r="B149" s="43" t="s">
         <v>440</v>
       </c>
-      <c r="C149" s="48" t="s">
+      <c r="C149" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="D149" s="48" t="s">
+      <c r="D149" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="E149" s="48" t="str">
+      <c r="E149" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
         <v>Inadequate Warning System</v>
       </c>
-      <c r="F149" s="49">
+      <c r="F149" s="45">
         <v>46296</v>
       </c>
-      <c r="G149" s="49" t="str">
+      <c r="G149" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -48068,46 +48449,46 @@
 ))</f>
         <v>W25 (26/9 - 2/10)</v>
       </c>
-      <c r="H149" s="49">
+      <c r="H149" s="45">
         <v>46296</v>
       </c>
-      <c r="I149" s="51" t="s">
+      <c r="I149" s="47" t="s">
         <v>199</v>
       </c>
-      <c r="J149" s="48" t="s">
+      <c r="J149" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="K149" s="48" t="s">
+      <c r="K149" s="44" t="s">
         <v>193</v>
       </c>
-      <c r="L149" s="52" t="s">
+      <c r="L149" s="48" t="s">
         <v>441</v>
       </c>
-      <c r="M149" s="53" t="s">
+      <c r="M149" s="49" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="150" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="47">
+      <c r="A150" s="43">
         <v>149</v>
       </c>
-      <c r="B150" s="47" t="s">
+      <c r="B150" s="43" t="s">
         <v>442</v>
       </c>
-      <c r="C150" s="48" t="s">
+      <c r="C150" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="D150" s="48" t="s">
+      <c r="D150" s="44" t="s">
         <v>429</v>
       </c>
-      <c r="E150" s="48" t="str">
+      <c r="E150" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
         <v>Inadequate or Improper Protective</v>
       </c>
-      <c r="F150" s="49">
+      <c r="F150" s="45">
         <v>46296</v>
       </c>
-      <c r="G150" s="49" t="str">
+      <c r="G150" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -48116,46 +48497,46 @@
 ))</f>
         <v>W25 (26/9 - 2/10)</v>
       </c>
-      <c r="H150" s="49">
+      <c r="H150" s="45">
         <v>46296</v>
       </c>
-      <c r="I150" s="51" t="s">
+      <c r="I150" s="47" t="s">
         <v>199</v>
       </c>
-      <c r="J150" s="48" t="s">
+      <c r="J150" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="K150" s="48" t="s">
+      <c r="K150" s="44" t="s">
         <v>193</v>
       </c>
-      <c r="L150" s="52" t="s">
+      <c r="L150" s="48" t="s">
         <v>443</v>
       </c>
-      <c r="M150" s="53" t="s">
+      <c r="M150" s="49" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="151" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="47">
+      <c r="A151" s="43">
         <v>150</v>
       </c>
-      <c r="B151" s="47" t="s">
+      <c r="B151" s="43" t="s">
         <v>444</v>
       </c>
-      <c r="C151" s="48" t="s">
+      <c r="C151" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="D151" s="48" t="s">
+      <c r="D151" s="44" t="s">
         <v>429</v>
       </c>
-      <c r="E151" s="48" t="str">
+      <c r="E151" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
         <v>Inadequate or Improper Protective</v>
       </c>
-      <c r="F151" s="49">
+      <c r="F151" s="45">
         <v>46296</v>
       </c>
-      <c r="G151" s="49" t="str">
+      <c r="G151" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -48164,46 +48545,46 @@
 ))</f>
         <v>W25 (26/9 - 2/10)</v>
       </c>
-      <c r="H151" s="49">
+      <c r="H151" s="45">
         <v>46296</v>
       </c>
-      <c r="I151" s="51" t="s">
+      <c r="I151" s="47" t="s">
         <v>230</v>
       </c>
-      <c r="J151" s="48" t="s">
+      <c r="J151" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="K151" s="48" t="s">
+      <c r="K151" s="44" t="s">
         <v>193</v>
       </c>
-      <c r="L151" s="52" t="s">
+      <c r="L151" s="48" t="s">
         <v>445</v>
       </c>
-      <c r="M151" s="53" t="s">
+      <c r="M151" s="49" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="152" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="47">
+      <c r="A152" s="43">
         <v>151</v>
       </c>
-      <c r="B152" s="47" t="s">
+      <c r="B152" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="C152" s="48" t="s">
+      <c r="C152" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="D152" s="48" t="s">
+      <c r="D152" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="E152" s="48" t="str">
+      <c r="E152" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
         <v>Safe Condition</v>
       </c>
-      <c r="F152" s="49">
+      <c r="F152" s="45">
         <v>46297</v>
       </c>
-      <c r="G152" s="49" t="str">
+      <c r="G152" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -48212,46 +48593,46 @@
 ))</f>
         <v>W25 (26/9 - 2/10)</v>
       </c>
-      <c r="H152" s="49">
+      <c r="H152" s="45">
         <v>46297</v>
       </c>
-      <c r="I152" s="51" t="s">
+      <c r="I152" s="47" t="s">
         <v>237</v>
       </c>
-      <c r="J152" s="48" t="s">
+      <c r="J152" s="44" t="s">
         <v>168</v>
       </c>
-      <c r="K152" s="48" t="s">
+      <c r="K152" s="44" t="s">
         <v>175</v>
       </c>
-      <c r="L152" s="52" t="s">
+      <c r="L152" s="48" t="s">
         <v>447</v>
       </c>
-      <c r="M152" s="53" t="s">
+      <c r="M152" s="49" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="47">
+      <c r="A153" s="43">
         <v>152</v>
       </c>
-      <c r="B153" s="47" t="s">
+      <c r="B153" s="43" t="s">
         <v>448</v>
       </c>
-      <c r="C153" s="48" t="s">
+      <c r="C153" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="D153" s="48" t="s">
+      <c r="D153" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="E153" s="48" t="str">
+      <c r="E153" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
         <v>Safe Condition</v>
       </c>
-      <c r="F153" s="49">
+      <c r="F153" s="45">
         <v>46297</v>
       </c>
-      <c r="G153" s="49" t="str">
+      <c r="G153" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -48260,46 +48641,46 @@
 ))</f>
         <v>W25 (26/9 - 2/10)</v>
       </c>
-      <c r="H153" s="49">
+      <c r="H153" s="45">
         <v>46297</v>
       </c>
-      <c r="I153" s="51" t="s">
+      <c r="I153" s="47" t="s">
         <v>331</v>
       </c>
-      <c r="J153" s="48" t="s">
+      <c r="J153" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="K153" s="48" t="s">
+      <c r="K153" s="44" t="s">
         <v>193</v>
       </c>
-      <c r="L153" s="52" t="s">
+      <c r="L153" s="48" t="s">
         <v>449</v>
       </c>
-      <c r="M153" s="53" t="s">
+      <c r="M153" s="49" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="154" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="47">
+      <c r="A154" s="43">
         <v>153</v>
       </c>
-      <c r="B154" s="47" t="s">
+      <c r="B154" s="43" t="s">
         <v>450</v>
       </c>
-      <c r="C154" s="48" t="s">
+      <c r="C154" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="D154" s="48" t="s">
+      <c r="D154" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="E154" s="48" t="str">
+      <c r="E154" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
         <v>Safe Condition</v>
       </c>
-      <c r="F154" s="49">
+      <c r="F154" s="45">
         <v>46297</v>
       </c>
-      <c r="G154" s="49" t="str">
+      <c r="G154" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -48308,46 +48689,46 @@
 ))</f>
         <v>W25 (26/9 - 2/10)</v>
       </c>
-      <c r="H154" s="49">
+      <c r="H154" s="45">
         <v>46297</v>
       </c>
-      <c r="I154" s="51" t="s">
+      <c r="I154" s="47" t="s">
         <v>451</v>
       </c>
-      <c r="J154" s="48" t="s">
+      <c r="J154" s="44" t="s">
         <v>168</v>
       </c>
-      <c r="K154" s="48" t="s">
+      <c r="K154" s="44" t="s">
         <v>169</v>
       </c>
-      <c r="L154" s="52" t="s">
+      <c r="L154" s="48" t="s">
         <v>452</v>
       </c>
-      <c r="M154" s="53" t="s">
+      <c r="M154" s="49" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="155" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="47">
+      <c r="A155" s="43">
         <v>154</v>
       </c>
-      <c r="B155" s="47" t="s">
+      <c r="B155" s="43" t="s">
         <v>453</v>
       </c>
-      <c r="C155" s="48" t="s">
+      <c r="C155" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="D155" s="48" t="s">
+      <c r="D155" s="44" t="s">
         <v>429</v>
       </c>
-      <c r="E155" s="48" t="str">
+      <c r="E155" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
         <v>Inadequate or Improper Protective</v>
       </c>
-      <c r="F155" s="49">
+      <c r="F155" s="45">
         <v>46297</v>
       </c>
-      <c r="G155" s="49" t="str">
+      <c r="G155" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -48356,46 +48737,46 @@
 ))</f>
         <v>W25 (26/9 - 2/10)</v>
       </c>
-      <c r="H155" s="49">
+      <c r="H155" s="45">
         <v>46297</v>
       </c>
-      <c r="I155" s="51" t="s">
+      <c r="I155" s="47" t="s">
         <v>217</v>
       </c>
-      <c r="J155" s="48" t="s">
+      <c r="J155" s="44" t="s">
         <v>168</v>
       </c>
-      <c r="K155" s="48" t="s">
+      <c r="K155" s="44" t="s">
         <v>169</v>
       </c>
-      <c r="L155" s="52" t="s">
+      <c r="L155" s="48" t="s">
         <v>454</v>
       </c>
-      <c r="M155" s="53" t="s">
+      <c r="M155" s="49" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="156" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="47">
+      <c r="A156" s="43">
         <v>155</v>
       </c>
-      <c r="B156" s="47" t="s">
+      <c r="B156" s="43" t="s">
         <v>455</v>
       </c>
-      <c r="C156" s="48" t="s">
+      <c r="C156" s="44" t="s">
         <v>149</v>
       </c>
-      <c r="D156" s="48" t="s">
+      <c r="D156" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="E156" s="48" t="str">
+      <c r="E156" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
         <v>Safe Act</v>
       </c>
-      <c r="F156" s="49">
+      <c r="F156" s="45">
         <v>46297</v>
       </c>
-      <c r="G156" s="49" t="str">
+      <c r="G156" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -48404,46 +48785,46 @@
 ))</f>
         <v>W25 (26/9 - 2/10)</v>
       </c>
-      <c r="H156" s="49">
+      <c r="H156" s="45">
         <v>46297</v>
       </c>
-      <c r="I156" s="51" t="s">
+      <c r="I156" s="47" t="s">
         <v>456</v>
       </c>
-      <c r="J156" s="48" t="s">
+      <c r="J156" s="44" t="s">
         <v>168</v>
       </c>
-      <c r="K156" s="48" t="s">
+      <c r="K156" s="44" t="s">
         <v>169</v>
       </c>
-      <c r="L156" s="52" t="s">
+      <c r="L156" s="48" t="s">
         <v>457</v>
       </c>
-      <c r="M156" s="53" t="s">
+      <c r="M156" s="49" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="157" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="47">
+      <c r="A157" s="43">
         <v>156</v>
       </c>
-      <c r="B157" s="47" t="s">
+      <c r="B157" s="43" t="s">
         <v>458</v>
       </c>
-      <c r="C157" s="48" t="s">
+      <c r="C157" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="D157" s="48" t="s">
+      <c r="D157" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="E157" s="48" t="str">
+      <c r="E157" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
         <v>Others - Hazardous Environmental Condition</v>
       </c>
-      <c r="F157" s="49">
+      <c r="F157" s="45">
         <v>46297</v>
       </c>
-      <c r="G157" s="49" t="str">
+      <c r="G157" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -48452,46 +48833,46 @@
 ))</f>
         <v>W25 (26/9 - 2/10)</v>
       </c>
-      <c r="H157" s="49">
+      <c r="H157" s="45">
         <v>46297</v>
       </c>
-      <c r="I157" s="51" t="s">
+      <c r="I157" s="47" t="s">
         <v>262</v>
       </c>
-      <c r="J157" s="48" t="s">
+      <c r="J157" s="44" t="s">
         <v>168</v>
       </c>
-      <c r="K157" s="48" t="s">
+      <c r="K157" s="44" t="s">
         <v>169</v>
       </c>
-      <c r="L157" s="52" t="s">
+      <c r="L157" s="48" t="s">
         <v>459</v>
       </c>
-      <c r="M157" s="53" t="s">
+      <c r="M157" s="49" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="158" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="47">
+      <c r="A158" s="43">
         <v>157</v>
       </c>
-      <c r="B158" s="47" t="s">
+      <c r="B158" s="43" t="s">
         <v>460</v>
       </c>
-      <c r="C158" s="48" t="s">
+      <c r="C158" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="D158" s="48" t="s">
+      <c r="D158" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="E158" s="48" t="str">
+      <c r="E158" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
         <v>Safe Condition</v>
       </c>
-      <c r="F158" s="49">
+      <c r="F158" s="45">
         <v>46297</v>
       </c>
-      <c r="G158" s="49" t="str">
+      <c r="G158" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -48500,46 +48881,46 @@
 ))</f>
         <v>W25 (26/9 - 2/10)</v>
       </c>
-      <c r="H158" s="49">
+      <c r="H158" s="45">
         <v>46297</v>
       </c>
-      <c r="I158" s="51" t="s">
+      <c r="I158" s="47" t="s">
         <v>237</v>
       </c>
-      <c r="J158" s="48" t="s">
+      <c r="J158" s="44" t="s">
         <v>168</v>
       </c>
-      <c r="K158" s="48" t="s">
+      <c r="K158" s="44" t="s">
         <v>175</v>
       </c>
-      <c r="L158" s="52" t="s">
+      <c r="L158" s="48" t="s">
         <v>461</v>
       </c>
-      <c r="M158" s="53" t="s">
+      <c r="M158" s="49" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="159" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="47">
+      <c r="A159" s="43">
         <v>158</v>
       </c>
-      <c r="B159" s="47" t="s">
+      <c r="B159" s="43" t="s">
         <v>462</v>
       </c>
-      <c r="C159" s="48" t="s">
+      <c r="C159" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="D159" s="48" t="s">
+      <c r="D159" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="E159" s="48" t="str">
+      <c r="E159" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
         <v>Safe Condition</v>
       </c>
-      <c r="F159" s="49">
+      <c r="F159" s="45">
         <v>46297</v>
       </c>
-      <c r="G159" s="49" t="str">
+      <c r="G159" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -48548,46 +48929,46 @@
 ))</f>
         <v>W25 (26/9 - 2/10)</v>
       </c>
-      <c r="H159" s="49">
+      <c r="H159" s="45">
         <v>46297</v>
       </c>
-      <c r="I159" s="51" t="s">
+      <c r="I159" s="47" t="s">
         <v>463</v>
       </c>
-      <c r="J159" s="48" t="s">
+      <c r="J159" s="44" t="s">
         <v>168</v>
       </c>
-      <c r="K159" s="48" t="s">
+      <c r="K159" s="44" t="s">
         <v>169</v>
       </c>
-      <c r="L159" s="52" t="s">
+      <c r="L159" s="48" t="s">
         <v>464</v>
       </c>
-      <c r="M159" s="53" t="s">
+      <c r="M159" s="49" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="160" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="47">
+      <c r="A160" s="43">
         <v>159</v>
       </c>
-      <c r="B160" s="47" t="s">
+      <c r="B160" s="43" t="s">
         <v>465</v>
       </c>
-      <c r="C160" s="48" t="s">
+      <c r="C160" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="D160" s="48" t="s">
+      <c r="D160" s="44" t="s">
         <v>95</v>
       </c>
-      <c r="E160" s="48" t="str">
+      <c r="E160" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
         <v>Inadequate Guards or Barriers</v>
       </c>
-      <c r="F160" s="49">
+      <c r="F160" s="45">
         <v>46297</v>
       </c>
-      <c r="G160" s="49" t="str">
+      <c r="G160" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -48596,46 +48977,46 @@
 ))</f>
         <v>W25 (26/9 - 2/10)</v>
       </c>
-      <c r="H160" s="49">
+      <c r="H160" s="45">
         <v>46297</v>
       </c>
-      <c r="I160" s="51" t="s">
+      <c r="I160" s="47" t="s">
         <v>466</v>
       </c>
-      <c r="J160" s="48" t="s">
+      <c r="J160" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="K160" s="48" t="s">
+      <c r="K160" s="44" t="s">
         <v>175</v>
       </c>
-      <c r="L160" s="52" t="s">
+      <c r="L160" s="48" t="s">
         <v>467</v>
       </c>
-      <c r="M160" s="53" t="s">
+      <c r="M160" s="49" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="47">
+      <c r="A161" s="43">
         <v>160</v>
       </c>
-      <c r="B161" s="47" t="s">
+      <c r="B161" s="43" t="s">
         <v>468</v>
       </c>
-      <c r="C161" s="48" t="s">
+      <c r="C161" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="D161" s="48" t="s">
+      <c r="D161" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="E161" s="48" t="str">
+      <c r="E161" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
         <v>Inadequate Warning System</v>
       </c>
-      <c r="F161" s="49">
+      <c r="F161" s="45">
         <v>46297</v>
       </c>
-      <c r="G161" s="49" t="str">
+      <c r="G161" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -48644,46 +49025,46 @@
 ))</f>
         <v>W25 (26/9 - 2/10)</v>
       </c>
-      <c r="H161" s="49">
+      <c r="H161" s="45">
         <v>46297</v>
       </c>
-      <c r="I161" s="51" t="s">
+      <c r="I161" s="47" t="s">
         <v>469</v>
       </c>
-      <c r="J161" s="48" t="s">
+      <c r="J161" s="44" t="s">
         <v>168</v>
       </c>
-      <c r="K161" s="48" t="s">
+      <c r="K161" s="44" t="s">
         <v>175</v>
       </c>
-      <c r="L161" s="52" t="s">
+      <c r="L161" s="48" t="s">
         <v>470</v>
       </c>
-      <c r="M161" s="53" t="s">
+      <c r="M161" s="49" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="162" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="47">
+      <c r="A162" s="43">
         <v>161</v>
       </c>
-      <c r="B162" s="47" t="s">
+      <c r="B162" s="43" t="s">
         <v>471</v>
       </c>
-      <c r="C162" s="48" t="s">
+      <c r="C162" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="D162" s="48" t="s">
+      <c r="D162" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="E162" s="48" t="str">
+      <c r="E162" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
         <v>Others - Unsafe Condition</v>
       </c>
-      <c r="F162" s="49">
+      <c r="F162" s="45">
         <v>46297</v>
       </c>
-      <c r="G162" s="49" t="str">
+      <c r="G162" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -48692,46 +49073,46 @@
 ))</f>
         <v>W25 (26/9 - 2/10)</v>
       </c>
-      <c r="H162" s="49">
+      <c r="H162" s="45">
         <v>46296</v>
       </c>
-      <c r="I162" s="51" t="s">
+      <c r="I162" s="47" t="s">
         <v>472</v>
       </c>
-      <c r="J162" s="48" t="s">
+      <c r="J162" s="44" t="s">
         <v>168</v>
       </c>
-      <c r="K162" s="48" t="s">
+      <c r="K162" s="44" t="s">
         <v>193</v>
       </c>
-      <c r="L162" s="52" t="s">
+      <c r="L162" s="48" t="s">
         <v>473</v>
       </c>
-      <c r="M162" s="53" t="s">
+      <c r="M162" s="49" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="163" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="47">
+      <c r="A163" s="43">
         <v>162</v>
       </c>
-      <c r="B163" s="47" t="s">
+      <c r="B163" s="43" t="s">
         <v>474</v>
       </c>
-      <c r="C163" s="48" t="s">
+      <c r="C163" s="44" t="s">
         <v>149</v>
       </c>
-      <c r="D163" s="48" t="s">
+      <c r="D163" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="E163" s="48" t="str">
+      <c r="E163" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
         <v>Safe Act</v>
       </c>
-      <c r="F163" s="49">
+      <c r="F163" s="45">
         <v>46297</v>
       </c>
-      <c r="G163" s="49" t="str">
+      <c r="G163" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -48740,46 +49121,46 @@
 ))</f>
         <v>W25 (26/9 - 2/10)</v>
       </c>
-      <c r="H163" s="49">
+      <c r="H163" s="45">
         <v>46297</v>
       </c>
-      <c r="I163" s="51" t="s">
+      <c r="I163" s="47" t="s">
         <v>475</v>
       </c>
-      <c r="J163" s="48" t="s">
+      <c r="J163" s="44" t="s">
         <v>168</v>
       </c>
-      <c r="K163" s="48" t="s">
+      <c r="K163" s="44" t="s">
         <v>169</v>
       </c>
-      <c r="L163" s="52" t="s">
+      <c r="L163" s="48" t="s">
         <v>476</v>
       </c>
-      <c r="M163" s="53" t="s">
+      <c r="M163" s="49" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="47">
+      <c r="A164" s="43">
         <v>163</v>
       </c>
-      <c r="B164" s="47" t="s">
+      <c r="B164" s="43" t="s">
         <v>477</v>
       </c>
-      <c r="C164" s="48" t="s">
+      <c r="C164" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="D164" s="48" t="s">
+      <c r="D164" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="E164" s="48" t="str">
+      <c r="E164" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
         <v>Suggestion for Improvement</v>
       </c>
-      <c r="F164" s="49">
+      <c r="F164" s="45">
         <v>46297</v>
       </c>
-      <c r="G164" s="49" t="str">
+      <c r="G164" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -48788,46 +49169,46 @@
 ))</f>
         <v>W25 (26/9 - 2/10)</v>
       </c>
-      <c r="H164" s="49">
+      <c r="H164" s="45">
         <v>46296</v>
       </c>
-      <c r="I164" s="51" t="s">
+      <c r="I164" s="47" t="s">
         <v>478</v>
       </c>
-      <c r="J164" s="48" t="s">
+      <c r="J164" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="K164" s="48" t="s">
+      <c r="K164" s="44" t="s">
         <v>175</v>
       </c>
-      <c r="L164" s="52" t="s">
+      <c r="L164" s="48" t="s">
         <v>479</v>
       </c>
-      <c r="M164" s="53" t="s">
+      <c r="M164" s="49" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="165" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="47">
+      <c r="A165" s="43">
         <v>164</v>
       </c>
-      <c r="B165" s="47" t="s">
+      <c r="B165" s="43" t="s">
         <v>480</v>
       </c>
-      <c r="C165" s="48" t="s">
+      <c r="C165" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="D165" s="48" t="s">
+      <c r="D165" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="E165" s="48" t="str">
+      <c r="E165" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
         <v>Safe Condition</v>
       </c>
-      <c r="F165" s="49">
+      <c r="F165" s="45">
         <v>46297</v>
       </c>
-      <c r="G165" s="49" t="str">
+      <c r="G165" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -48836,46 +49217,46 @@
 ))</f>
         <v>W25 (26/9 - 2/10)</v>
       </c>
-      <c r="H165" s="49">
+      <c r="H165" s="45">
         <v>46297</v>
       </c>
-      <c r="I165" s="51" t="s">
+      <c r="I165" s="47" t="s">
         <v>481</v>
       </c>
-      <c r="J165" s="48" t="s">
+      <c r="J165" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="K165" s="48" t="s">
+      <c r="K165" s="44" t="s">
         <v>175</v>
       </c>
-      <c r="L165" s="52" t="s">
+      <c r="L165" s="48" t="s">
         <v>482</v>
       </c>
-      <c r="M165" s="53" t="s">
+      <c r="M165" s="49" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="47">
+      <c r="A166" s="43">
         <v>165</v>
       </c>
-      <c r="B166" s="47" t="s">
+      <c r="B166" s="43" t="s">
         <v>483</v>
       </c>
-      <c r="C166" s="48" t="s">
+      <c r="C166" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="D166" s="48" t="s">
+      <c r="D166" s="44" t="s">
         <v>95</v>
       </c>
-      <c r="E166" s="48" t="str">
+      <c r="E166" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
         <v>Inadequate Guards or Barriers</v>
       </c>
-      <c r="F166" s="49">
+      <c r="F166" s="45">
         <v>46297</v>
       </c>
-      <c r="G166" s="49" t="str">
+      <c r="G166" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -48884,46 +49265,46 @@
 ))</f>
         <v>W25 (26/9 - 2/10)</v>
       </c>
-      <c r="H166" s="49">
+      <c r="H166" s="45">
         <v>46297</v>
       </c>
-      <c r="I166" s="51" t="s">
+      <c r="I166" s="47" t="s">
         <v>478</v>
       </c>
-      <c r="J166" s="48" t="s">
+      <c r="J166" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="K166" s="48" t="s">
+      <c r="K166" s="44" t="s">
         <v>175</v>
       </c>
-      <c r="L166" s="52" t="s">
+      <c r="L166" s="48" t="s">
         <v>484</v>
       </c>
-      <c r="M166" s="53" t="s">
+      <c r="M166" s="49" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="167" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="47">
+      <c r="A167" s="43">
         <v>166</v>
       </c>
-      <c r="B167" s="47" t="s">
+      <c r="B167" s="43" t="s">
         <v>485</v>
       </c>
-      <c r="C167" s="48" t="s">
+      <c r="C167" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="D167" s="48" t="s">
+      <c r="D167" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="E167" s="48" t="str">
+      <c r="E167" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
         <v>Suggestion for Improvement</v>
       </c>
-      <c r="F167" s="49">
+      <c r="F167" s="45">
         <v>46297</v>
       </c>
-      <c r="G167" s="49" t="str">
+      <c r="G167" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -48932,46 +49313,46 @@
 ))</f>
         <v>W25 (26/9 - 2/10)</v>
       </c>
-      <c r="H167" s="49">
+      <c r="H167" s="45">
         <v>46297</v>
       </c>
-      <c r="I167" s="51" t="s">
+      <c r="I167" s="47" t="s">
         <v>199</v>
       </c>
-      <c r="J167" s="48" t="s">
+      <c r="J167" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="K167" s="48" t="s">
+      <c r="K167" s="44" t="s">
         <v>193</v>
       </c>
-      <c r="L167" s="52" t="s">
+      <c r="L167" s="48" t="s">
         <v>486</v>
       </c>
-      <c r="M167" s="53" t="s">
+      <c r="M167" s="49" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="168" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="47">
+      <c r="A168" s="43">
         <v>167</v>
       </c>
-      <c r="B168" s="47" t="s">
+      <c r="B168" s="43" t="s">
         <v>487</v>
       </c>
-      <c r="C168" s="48" t="s">
+      <c r="C168" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="D168" s="48" t="s">
+      <c r="D168" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="E168" s="48" t="str">
+      <c r="E168" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
         <v>Others - Hazardous Environmental Condition</v>
       </c>
-      <c r="F168" s="49">
+      <c r="F168" s="45">
         <v>46297</v>
       </c>
-      <c r="G168" s="49" t="str">
+      <c r="G168" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -48980,46 +49361,46 @@
 ))</f>
         <v>W25 (26/9 - 2/10)</v>
       </c>
-      <c r="H168" s="49">
+      <c r="H168" s="45">
         <v>46297</v>
       </c>
-      <c r="I168" s="51" t="s">
+      <c r="I168" s="47" t="s">
         <v>199</v>
       </c>
-      <c r="J168" s="48" t="s">
+      <c r="J168" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="K168" s="48" t="s">
+      <c r="K168" s="44" t="s">
         <v>193</v>
       </c>
-      <c r="L168" s="52" t="s">
+      <c r="L168" s="48" t="s">
         <v>488</v>
       </c>
-      <c r="M168" s="53" t="s">
+      <c r="M168" s="49" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="169" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="47">
+      <c r="A169" s="43">
         <v>168</v>
       </c>
-      <c r="B169" s="47" t="s">
+      <c r="B169" s="43" t="s">
         <v>489</v>
       </c>
-      <c r="C169" s="48" t="s">
+      <c r="C169" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="D169" s="48" t="s">
+      <c r="D169" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="E169" s="48" t="str">
+      <c r="E169" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
         <v>Others - Hazardous Environmental Condition</v>
       </c>
-      <c r="F169" s="49">
+      <c r="F169" s="45">
         <v>46297</v>
       </c>
-      <c r="G169" s="49" t="str">
+      <c r="G169" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -49028,46 +49409,46 @@
 ))</f>
         <v>W25 (26/9 - 2/10)</v>
       </c>
-      <c r="H169" s="49">
+      <c r="H169" s="45">
         <v>46297</v>
       </c>
-      <c r="I169" s="51" t="s">
+      <c r="I169" s="47" t="s">
         <v>81</v>
       </c>
-      <c r="J169" s="48" t="s">
+      <c r="J169" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="K169" s="48" t="s">
+      <c r="K169" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="L169" s="52" t="s">
+      <c r="L169" s="48" t="s">
         <v>490</v>
       </c>
-      <c r="M169" s="53" t="s">
+      <c r="M169" s="49" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="170" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="47">
+      <c r="A170" s="43">
         <v>169</v>
       </c>
-      <c r="B170" s="47" t="s">
+      <c r="B170" s="43" t="s">
         <v>491</v>
       </c>
-      <c r="C170" s="48" t="s">
+      <c r="C170" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="D170" s="48" t="s">
+      <c r="D170" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="E170" s="48" t="str">
+      <c r="E170" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
         <v>Safe Condition</v>
       </c>
-      <c r="F170" s="49">
+      <c r="F170" s="45">
         <v>46297</v>
       </c>
-      <c r="G170" s="49" t="str">
+      <c r="G170" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -49076,22 +49457,22 @@
 ))</f>
         <v>W25 (26/9 - 2/10)</v>
       </c>
-      <c r="H170" s="49">
+      <c r="H170" s="45">
         <v>46297</v>
       </c>
-      <c r="I170" s="51" t="s">
+      <c r="I170" s="47" t="s">
         <v>492</v>
       </c>
-      <c r="J170" s="48" t="s">
+      <c r="J170" s="44" t="s">
         <v>168</v>
       </c>
-      <c r="K170" s="48" t="s">
+      <c r="K170" s="44" t="s">
         <v>169</v>
       </c>
-      <c r="L170" s="52" t="s">
+      <c r="L170" s="48" t="s">
         <v>493</v>
       </c>
-      <c r="M170" s="53" t="s">
+      <c r="M170" s="49" t="s">
         <v>75</v>
       </c>
     </row>

--- a/HSE Dashboard Rev 0(3).xlsx
+++ b/HSE Dashboard Rev 0(3).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://databasehub-my.sharepoint.com/personal/hse_databasehub_onmicrosoft_com/Documents/POM HSE DOCUMENTATION/DASHBOARD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="123" documentId="11_50060B46BD35296F53D3E59C33CD99FCCDC13A9C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D182131-B968-4B26-AF5D-ED659C8F05EB}"/>
+  <xr:revisionPtr revIDLastSave="132" documentId="11_50060B46BD35296F53D3E59C33CD99FCCDC13A9C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D24B1410-3A57-44EE-BD64-4ECBAC1016A6}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="105" yWindow="1980" windowWidth="28800" windowHeight="15345" firstSheet="9" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="9" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POM_Office" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4649" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4654" uniqueCount="522">
   <si>
     <t>DATE</t>
   </si>
@@ -1622,6 +1622,15 @@
   <si>
     <t>W25 (26/9 - 2/10)</t>
   </si>
+  <si>
+    <t>radhzmir</t>
+  </si>
+  <si>
+    <t>12345679</t>
+  </si>
+  <si>
+    <t>Mohd Radhzmir binMohd Aziz</t>
+  </si>
 </sst>
 </file>
 
@@ -1633,7 +1642,7 @@
     <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="167" formatCode="dd\-mmm\-yyyy;@"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1697,6 +1706,12 @@
       <color rgb="FF000000"/>
       <name val="Arial Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1931,7 +1946,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2078,9 +2093,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2111,28 +2123,12 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial Narrow"/>
         <family val="2"/>
       </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -2142,28 +2138,12 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial Narrow"/>
         <family val="2"/>
       </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom/>
-      </border>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -2173,21 +2153,40 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial Narrow"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial Narrow"/>
         <family val="2"/>
       </font>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border>
         <left style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
         <vertical/>
         <horizontal/>
       </border>
@@ -2200,21 +2199,38 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial Narrow"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial Narrow"/>
         <family val="2"/>
       </font>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border>
         <left style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </left>
         <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
+        <top style="hair">
+          <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
         <vertical/>
         <horizontal/>
       </border>
@@ -2227,86 +2243,25 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Arial"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial Narrow"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="167" formatCode="dd\-mmm\-yyyy;@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border>
         <left style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
         <vertical/>
         <horizontal/>
       </border>
@@ -2319,28 +2274,23 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Arial"/>
+        <name val="Arial Narrow"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border outline="0">
         <left style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </left>
         <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
+        <top style="hair">
+          <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -2351,30 +2301,25 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial Narrow"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
+      <border outline="0">
         <left style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
         </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -2385,27 +2330,26 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial Narrow"/>
         <family val="2"/>
       </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border outline="0">
         <left style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -2416,27 +2360,26 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial Narrow"/>
         <family val="2"/>
       </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="164" formatCode="dddd"/>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border outline="0">
         <left style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -2447,58 +2390,24 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Arial"/>
+        <name val="Arial Narrow"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border outline="0">
         <left/>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="hair">
+          <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="hair">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -2512,6 +2421,9 @@
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
+        <bottom style="hair">
+          <color rgb="FF000000"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -2522,18 +2434,19 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Arial"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial Narrow"/>
         <family val="2"/>
       </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2544,18 +2457,24 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="0"/>
-        <name val="Arial"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial Narrow"/>
         <family val="2"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border outline="0">
         <left style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </right>
         <top/>
         <bottom/>
@@ -7394,12 +7313,28 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial Narrow"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
         <family val="2"/>
       </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -7409,12 +7344,28 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial Narrow"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
         <family val="2"/>
       </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -7424,40 +7375,21 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial Narrow"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial Narrow"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
         <family val="2"/>
       </font>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border>
         <left style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
         </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
@@ -7470,38 +7402,21 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial Narrow"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial Narrow"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
         <family val="2"/>
       </font>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border>
         <left style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </left>
         <right/>
-        <top style="hair">
-          <color indexed="64"/>
+        <top style="thin">
+          <color rgb="FF000000"/>
         </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
@@ -7514,25 +7429,86 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial Narrow"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Arial"/>
         <family val="2"/>
       </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <numFmt numFmtId="167" formatCode="dd\-mmm\-yyyy;@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <border>
         <left style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
         </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
         <vertical/>
         <horizontal/>
       </border>
@@ -7545,23 +7521,28 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
+        <sz val="9"/>
         <color theme="1"/>
-        <name val="Arial Narrow"/>
+        <name val="Arial"/>
         <family val="2"/>
       </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <border outline="0">
         <left style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </left>
         <right/>
-        <top style="hair">
-          <color indexed="64"/>
+        <top style="thin">
+          <color rgb="FF000000"/>
         </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -7572,25 +7553,30 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial Narrow"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
         <family val="2"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border outline="0">
+      <border>
         <left style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
         </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -7601,26 +7587,27 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial Narrow"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border outline="0">
         <left style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
         </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -7631,26 +7618,27 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial Narrow"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="164" formatCode="dddd"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border outline="0">
         <left style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
         </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -7661,24 +7649,58 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
+        <sz val="9"/>
         <color theme="1"/>
-        <name val="Arial Narrow"/>
+        <name val="Arial"/>
         <family val="2"/>
       </font>
-      <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <border outline="0">
         <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="hair">
-          <color indexed="64"/>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
         </top>
-        <bottom style="hair">
-          <color indexed="64"/>
-        </bottom>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -7692,9 +7714,6 @@
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
-        <bottom style="hair">
-          <color rgb="FF000000"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -7705,19 +7724,18 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial Narrow"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Arial"/>
         <family val="2"/>
       </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </dxf>
     <dxf>
       <font>
@@ -7728,24 +7746,18 @@
         <outline val="0"/>
         <shadow val="0"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial Narrow"/>
+        <sz val="9"/>
+        <color theme="0"/>
+        <name val="Arial"/>
         <family val="2"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <border outline="0">
         <left style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </left>
         <right style="thin">
-          <color indexed="64"/>
+          <color rgb="FF000000"/>
         </right>
         <top/>
         <bottom/>
@@ -7970,18 +7982,24 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{00000000-000C-0000-FFFF-FFFF10000000}" name="Table3" displayName="Table3" ref="A1:M170" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15" tableBorderDxfId="14">
-  <autoFilter ref="A1:M170" xr:uid="{00000000-0009-0000-0100-000011000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{00000000-000C-0000-FFFF-FFFF10000000}" name="Table3" displayName="Table3" ref="A1:M170" totalsRowShown="0" headerRowDxfId="223" dataDxfId="222" tableBorderDxfId="221">
+  <autoFilter ref="A1:M170" xr:uid="{00000000-0009-0000-0100-000011000000}">
+    <filterColumn colId="5">
+      <filters>
+        <dateGroupItem year="2026" month="9" dateTimeGrouping="month"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1000-000001000000}" name="No" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1000-000002000000}" name="BSC No" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1000-000003000000}" name="BSC Type" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1000-000004000000}" name="Hazard Type RAW" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-1000-00000A000000}" name="Hazard Type" dataDxfId="9">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1000-000001000000}" name="No" dataDxfId="220"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1000-000002000000}" name="BSC No" dataDxfId="219"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1000-000003000000}" name="BSC Type" dataDxfId="218"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1000-000004000000}" name="Hazard Type RAW" dataDxfId="217"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-1000-00000A000000}" name="Hazard Type" dataDxfId="216">
       <calculatedColumnFormula>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1000-000005000000}" name="Date Reported" dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-1000-00000B000000}" name="Week" dataDxfId="7" dataCellStyle="Normal 2">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1000-000005000000}" name="Date Reported" dataDxfId="215"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-1000-00000B000000}" name="Week" dataDxfId="214" dataCellStyle="Normal 2">
       <calculatedColumnFormula>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -7989,26 +8007,26 @@
 "W"&amp;TEXT(_xlpm.W,"00")&amp;" ("&amp;TEXT(_xlpm.S,"d/m")&amp;" - "&amp;TEXT(_xlpm.E,"d/m")&amp;")"
 ))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1000-000006000000}" name="Date Observed" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-1000-000007000000}" name="Observed By" dataDxfId="5"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-1000-00000C000000}" name="Company" dataDxfId="4" dataCellStyle="Normal 2"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-1000-00000D000000}" name="Position" dataDxfId="3" dataCellStyle="Normal 2"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-1000-000008000000}" name="What and where hazard/act observed and_x000a_discussed with worker/supervisor/manager?" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-1000-000009000000}" name="Status" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1000-000006000000}" name="Date Observed" dataDxfId="213"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-1000-000007000000}" name="Observed By" dataDxfId="212"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-1000-00000C000000}" name="Company" dataDxfId="211" dataCellStyle="Normal 2"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-1000-00000D000000}" name="Position" dataDxfId="210" dataCellStyle="Normal 2"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-1000-000008000000}" name="What and where hazard/act observed and_x000a_discussed with worker/supervisor/manager?" dataDxfId="209"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-1000-000009000000}" name="Status" dataDxfId="208"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{00000000-000C-0000-FFFF-FFFF11000000}" name="Leading20" displayName="Leading20" ref="A5:L176" totalsRowShown="0" headerRowDxfId="223" dataDxfId="221" headerRowBorderDxfId="222" tableBorderDxfId="220">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{00000000-000C-0000-FFFF-FFFF11000000}" name="Leading20" displayName="Leading20" ref="A5:L176" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13">
   <autoFilter ref="A5:L176" xr:uid="{00000000-0009-0000-0100-000012000000}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1100-000001000000}" name="DATE" dataDxfId="219"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1100-000002000000}" name="DAY" dataDxfId="218">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1100-000001000000}" name="DATE" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1100-000002000000}" name="DAY" dataDxfId="11">
       <calculatedColumnFormula>A6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1100-000003000000}" name="WEEK" dataDxfId="217">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1100-000003000000}" name="WEEK" dataDxfId="10">
       <calculatedColumnFormula>IF(Leading20[[#This Row],[DATE]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Leading20[[#This Row],[DATE]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -8016,15 +8034,15 @@
 "W"&amp;TEXT(_xlpm.W,"00")&amp;" ("&amp;TEXT(_xlpm.S,"d/m")&amp;" - "&amp;TEXT(_xlpm.E,"d/m")&amp;")"
 ))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1100-000006000000}" name="SIC" dataDxfId="216"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-1100-000007000000}" name="PTW NOVADE" dataDxfId="215"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1100-000004000000}" name="EMERGENCY RESPONSE" dataDxfId="214"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1100-000005000000}" name="FIRE WATCH" dataDxfId="213"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-1100-000008000000}" name="CHEMICAL HANDLING" dataDxfId="212"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-1100-00000F000000}" name="WASTE MANAGEMENT" dataDxfId="211"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-1100-000009000000}" name="ELECTRICAL SAFETY" dataDxfId="210"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-1100-00000A000000}" name="PPE AWARENESS" dataDxfId="209"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-1100-00000B000000}" name="HAND TOOLS &amp; POWER TOOLS SAFETY" dataDxfId="208"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1100-000006000000}" name="SIC" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-1100-000007000000}" name="PTW NOVADE" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1100-000004000000}" name="EMERGENCY RESPONSE" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1100-000005000000}" name="FIRE WATCH" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-1100-000008000000}" name="CHEMICAL HANDLING" dataDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-1100-00000F000000}" name="WASTE MANAGEMENT" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-1100-000009000000}" name="ELECTRICAL SAFETY" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-1100-00000A000000}" name="PPE AWARENESS" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-1100-00000B000000}" name="HAND TOOLS &amp; POWER TOOLS SAFETY" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -40928,7 +40946,7 @@
         <f t="shared" ref="B172:B176" si="6">A172</f>
         <v>46291</v>
       </c>
-      <c r="C172" s="50" t="str">
+      <c r="C172" s="35" t="str">
         <f>IF(Leading[[#This Row],[DATE]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Leading[[#This Row],[DATE]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -40982,7 +41000,7 @@
         <f t="shared" si="6"/>
         <v>46292</v>
       </c>
-      <c r="C173" s="50" t="str">
+      <c r="C173" s="35" t="str">
         <f>IF(Leading[[#This Row],[DATE]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Leading[[#This Row],[DATE]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -41036,7 +41054,7 @@
         <f t="shared" si="6"/>
         <v>46293</v>
       </c>
-      <c r="C174" s="50" t="str">
+      <c r="C174" s="35" t="str">
         <f>IF(Leading[[#This Row],[DATE]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Leading[[#This Row],[DATE]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -41090,7 +41108,7 @@
         <f t="shared" si="6"/>
         <v>46294</v>
       </c>
-      <c r="C175" s="50" t="str">
+      <c r="C175" s="35" t="str">
         <f>IF(Leading[[#This Row],[DATE]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Leading[[#This Row],[DATE]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -41144,7 +41162,7 @@
         <f t="shared" si="6"/>
         <v>46295</v>
       </c>
-      <c r="C176" s="50" t="str">
+      <c r="C176" s="35" t="str">
         <f>IF(Leading[[#This Row],[DATE]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Leading[[#This Row],[DATE]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -41162,7 +41180,7 @@
       <c r="F176" s="35">
         <v>0</v>
       </c>
-      <c r="G176" s="52">
+      <c r="G176" s="51">
         <v>1</v>
       </c>
       <c r="H176" s="35">
@@ -41198,7 +41216,7 @@
         <f t="shared" ref="B177:B178" si="7">A177</f>
         <v>46296</v>
       </c>
-      <c r="C177" s="50" t="str">
+      <c r="C177" s="35" t="str">
         <f>IF(Leading[[#This Row],[DATE]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Leading[[#This Row],[DATE]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -41213,10 +41231,10 @@
       <c r="E177" s="35">
         <v>1</v>
       </c>
-      <c r="F177" s="51">
+      <c r="F177" s="50">
         <v>1</v>
       </c>
-      <c r="G177" s="52">
+      <c r="G177" s="51">
         <v>0</v>
       </c>
       <c r="H177" s="35">
@@ -41252,7 +41270,7 @@
         <f t="shared" si="7"/>
         <v>46297</v>
       </c>
-      <c r="C178" s="50" t="str">
+      <c r="C178" s="35" t="str">
         <f>IF(Leading[[#This Row],[DATE]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Leading[[#This Row],[DATE]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -41267,10 +41285,10 @@
       <c r="E178" s="35">
         <v>1</v>
       </c>
-      <c r="F178" s="51">
-        <v>0</v>
-      </c>
-      <c r="G178" s="52">
+      <c r="F178" s="50">
+        <v>0</v>
+      </c>
+      <c r="G178" s="51">
         <v>0</v>
       </c>
       <c r="H178" s="35">
@@ -41364,7 +41382,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16">
         <v>1</v>
       </c>
@@ -41412,7 +41430,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16">
         <v>2</v>
       </c>
@@ -41460,7 +41478,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16">
         <v>3</v>
       </c>
@@ -41508,7 +41526,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16">
         <v>4</v>
       </c>
@@ -41556,7 +41574,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16">
         <v>5</v>
       </c>
@@ -41604,7 +41622,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16">
         <v>6</v>
       </c>
@@ -41652,7 +41670,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
         <v>7</v>
       </c>
@@ -41700,7 +41718,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16">
         <v>8</v>
       </c>
@@ -41748,7 +41766,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16">
         <v>9</v>
       </c>
@@ -41796,7 +41814,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16">
         <v>10</v>
       </c>
@@ -41844,7 +41862,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16">
         <v>11</v>
       </c>
@@ -41892,7 +41910,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16">
         <v>12</v>
       </c>
@@ -41940,7 +41958,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16">
         <v>13</v>
       </c>
@@ -41988,7 +42006,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16">
         <v>14</v>
       </c>
@@ -42036,7 +42054,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16">
         <v>15</v>
       </c>
@@ -42084,7 +42102,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16">
         <v>16</v>
       </c>
@@ -42132,7 +42150,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16">
         <v>17</v>
       </c>
@@ -42180,7 +42198,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16">
         <v>18</v>
       </c>
@@ -42228,7 +42246,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16">
         <v>19</v>
       </c>
@@ -42276,7 +42294,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16">
         <v>20</v>
       </c>
@@ -42324,7 +42342,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16">
         <v>21</v>
       </c>
@@ -42372,7 +42390,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16">
         <v>22</v>
       </c>
@@ -42420,7 +42438,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16">
         <v>23</v>
       </c>
@@ -42468,7 +42486,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16">
         <v>24</v>
       </c>
@@ -42516,7 +42534,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16">
         <v>25</v>
       </c>
@@ -42564,7 +42582,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16">
         <v>26</v>
       </c>
@@ -42612,7 +42630,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16">
         <v>27</v>
       </c>
@@ -42660,7 +42678,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16">
         <v>28</v>
       </c>
@@ -42708,7 +42726,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16">
         <v>29</v>
       </c>
@@ -42756,7 +42774,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16">
         <v>30</v>
       </c>
@@ -42804,7 +42822,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="16">
         <v>31</v>
       </c>
@@ -42852,7 +42870,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16">
         <v>32</v>
       </c>
@@ -42900,7 +42918,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
         <v>33</v>
       </c>
@@ -42948,7 +42966,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
         <v>34</v>
       </c>
@@ -42996,7 +43014,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16">
         <v>35</v>
       </c>
@@ -43044,7 +43062,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="16">
         <v>36</v>
       </c>
@@ -43092,7 +43110,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="16">
         <v>37</v>
       </c>
@@ -43140,7 +43158,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="16">
         <v>38</v>
       </c>
@@ -43188,7 +43206,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="16">
         <v>39</v>
       </c>
@@ -43236,7 +43254,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="16">
         <v>40</v>
       </c>
@@ -43284,7 +43302,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="16">
         <v>41</v>
       </c>
@@ -43332,7 +43350,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="16">
         <v>42</v>
       </c>
@@ -48324,7 +48342,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="147" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="43">
         <v>146</v>
       </c>
@@ -48372,7 +48390,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="148" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="43">
         <v>147</v>
       </c>
@@ -48420,7 +48438,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="149" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="43">
         <v>148</v>
       </c>
@@ -48468,7 +48486,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="150" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="43">
         <v>149</v>
       </c>
@@ -48516,7 +48534,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="151" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="43">
         <v>150</v>
       </c>
@@ -48564,7 +48582,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="152" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="43">
         <v>151</v>
       </c>
@@ -48612,7 +48630,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="153" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="43">
         <v>152</v>
       </c>
@@ -48660,7 +48678,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="154" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="43">
         <v>153</v>
       </c>
@@ -48708,7 +48726,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="155" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="43">
         <v>154</v>
       </c>
@@ -48756,7 +48774,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="156" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="43">
         <v>155</v>
       </c>
@@ -48804,7 +48822,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="157" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="43">
         <v>156</v>
       </c>
@@ -48852,7 +48870,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="158" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="43">
         <v>157</v>
       </c>
@@ -48900,7 +48918,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="159" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="43">
         <v>158</v>
       </c>
@@ -48948,7 +48966,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="160" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="43">
         <v>159</v>
       </c>
@@ -48996,7 +49014,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="161" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="43">
         <v>160</v>
       </c>
@@ -49044,7 +49062,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="162" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="43">
         <v>161</v>
       </c>
@@ -49092,7 +49110,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="163" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="43">
         <v>162</v>
       </c>
@@ -49140,7 +49158,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="164" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="43">
         <v>163</v>
       </c>
@@ -49188,7 +49206,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="165" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="43">
         <v>164</v>
       </c>
@@ -49236,7 +49254,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="166" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="43">
         <v>165</v>
       </c>
@@ -49284,7 +49302,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="167" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="43">
         <v>166</v>
       </c>
@@ -49332,7 +49350,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="168" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="43">
         <v>167</v>
       </c>
@@ -49380,7 +49398,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="169" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="43">
         <v>168</v>
       </c>
@@ -49428,7 +49446,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="170" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="43">
         <v>169</v>
       </c>
@@ -57263,7 +57281,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -57357,8 +57375,26 @@
         <v>421</v>
       </c>
     </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>519</v>
+      </c>
+      <c r="B6" t="s">
+        <v>520</v>
+      </c>
+      <c r="C6" t="s">
+        <v>521</v>
+      </c>
+      <c r="D6" t="s">
+        <v>425</v>
+      </c>
+      <c r="E6" t="s">
+        <v>421</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E5" xr:uid="{00000000-0009-0000-0000-000012000000}"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/HSE Dashboard Rev 0(3).xlsx
+++ b/HSE Dashboard Rev 0(3).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://databasehub-my.sharepoint.com/personal/hse_databasehub_onmicrosoft_com/Documents/POM HSE DOCUMENTATION/DASHBOARD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="132" documentId="11_50060B46BD35296F53D3E59C33CD99FCCDC13A9C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D24B1410-3A57-44EE-BD64-4ECBAC1016A6}"/>
+  <xr:revisionPtr revIDLastSave="149" documentId="11_50060B46BD35296F53D3E59C33CD99FCCDC13A9C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E434D5B-D78A-4689-9099-3AAC492DFC55}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="9" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="9" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POM_Office" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4654" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4686" uniqueCount="532">
   <si>
     <t>DATE</t>
   </si>
@@ -1629,7 +1629,37 @@
     <t>12345679</t>
   </si>
   <si>
-    <t>Mohd Radhzmir binMohd Aziz</t>
+    <t>Mohd Radhzmir bin Mohd Aziz</t>
+  </si>
+  <si>
+    <t>BSC2026_15815</t>
+  </si>
+  <si>
+    <t>BSC2026_15816</t>
+  </si>
+  <si>
+    <t>BSC2026_15818</t>
+  </si>
+  <si>
+    <t>BSC2026_15862</t>
+  </si>
+  <si>
+    <t>Defective Tools, Equipment or Mat</t>
+  </si>
+  <si>
+    <t>Ismadi</t>
+  </si>
+  <si>
+    <t>Lifting rebar without padding/discussed with lifting supv n HSE penta to protect webbing sling from any sharp edge materials to lift</t>
+  </si>
+  <si>
+    <t>Demarcation between access way and working area on the barge</t>
+  </si>
+  <si>
+    <t>Tool box meeting before star work</t>
+  </si>
+  <si>
+    <t>pedistrian from parking area to gate</t>
   </si>
 </sst>
 </file>
@@ -1946,7 +1976,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2097,6 +2127,39 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2475,6 +2538,464 @@
         </left>
         <right style="thin">
           <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="167" formatCode="dd\-mmm\-yyyy;@"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <border outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
         </right>
         <top/>
         <bottom/>
@@ -7305,464 +7826,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="167" formatCode="dd\-mmm\-yyyy;@"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="dd\-mmm\-yyyy"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <border outline="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="0"/>
-        <name val="Arial"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -7781,32 +7844,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="POM" displayName="POM" ref="A5:G178" totalsRowShown="0" headerRowDxfId="207" dataDxfId="205" headerRowBorderDxfId="206" tableBorderDxfId="204">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="POM" displayName="POM" ref="A5:G178" totalsRowShown="0" headerRowDxfId="223" dataDxfId="221" headerRowBorderDxfId="222" tableBorderDxfId="220">
   <autoFilter ref="A5:G178" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="DATE" dataDxfId="203"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DAY" dataDxfId="202">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="DATE" dataDxfId="219"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DAY" dataDxfId="218">
       <calculatedColumnFormula>A6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="WEEK" dataDxfId="201"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="COMPANY" dataDxfId="200"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="CATEGORY" dataDxfId="199"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="MANDAY" dataDxfId="198"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="MANHOUR" dataDxfId="197"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="WEEK" dataDxfId="217"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="COMPANY" dataDxfId="216"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="CATEGORY" dataDxfId="215"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="MANDAY" dataDxfId="214"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="MANHOUR" dataDxfId="213"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="JK_HIDRO" displayName="JK_HIDRO" ref="A5:G79" totalsRowShown="0" headerRowDxfId="108" dataDxfId="106" headerRowBorderDxfId="107" tableBorderDxfId="105">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="JK_HIDRO" displayName="JK_HIDRO" ref="A5:G79" totalsRowShown="0" headerRowDxfId="124" dataDxfId="122" headerRowBorderDxfId="123" tableBorderDxfId="121">
   <autoFilter ref="A5:G79" xr:uid="{00000000-0009-0000-0100-00000A000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="DATE" dataDxfId="104"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="DAY" dataDxfId="103">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="DATE" dataDxfId="120"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="DAY" dataDxfId="119">
       <calculatedColumnFormula>A6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="WEEK" dataDxfId="102">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="WEEK" dataDxfId="118">
       <calculatedColumnFormula>IF(JK_HIDRO[[#This Row],[DATE]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((JK_HIDRO[[#This Row],[DATE]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -7814,24 +7877,24 @@
 "W"&amp;TEXT(_xlpm.W,"00")&amp;" ("&amp;TEXT(_xlpm.S,"d/m")&amp;" - "&amp;TEXT(_xlpm.E,"d/m")&amp;")"
 ))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="COMPANY" dataDxfId="101"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="CATEGORY" dataDxfId="100"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="MANDAY" dataDxfId="99"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0900-000007000000}" name="MANHOUR" dataDxfId="98"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="COMPANY" dataDxfId="117"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="CATEGORY" dataDxfId="116"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="MANDAY" dataDxfId="115"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0900-000007000000}" name="MANHOUR" dataDxfId="114"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{00000000-000C-0000-FFFF-FFFF0A000000}" name="SECURITY" displayName="SECURITY" ref="A5:G99" totalsRowShown="0" headerRowDxfId="97" dataDxfId="95" headerRowBorderDxfId="96" tableBorderDxfId="94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{00000000-000C-0000-FFFF-FFFF0A000000}" name="SECURITY" displayName="SECURITY" ref="A5:G99" totalsRowShown="0" headerRowDxfId="113" dataDxfId="111" headerRowBorderDxfId="112" tableBorderDxfId="110">
   <autoFilter ref="A5:G99" xr:uid="{00000000-0009-0000-0100-00000B000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0A00-000001000000}" name="DATE" dataDxfId="93"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0A00-000002000000}" name="DAY" dataDxfId="92">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0A00-000001000000}" name="DATE" dataDxfId="109"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0A00-000002000000}" name="DAY" dataDxfId="108">
       <calculatedColumnFormula>A6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0A00-000003000000}" name="WEEK" dataDxfId="91">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0A00-000003000000}" name="WEEK" dataDxfId="107">
       <calculatedColumnFormula>IF(SECURITY[[#This Row],[DATE]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((SECURITY[[#This Row],[DATE]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -7839,42 +7902,42 @@
 "W"&amp;TEXT(_xlpm.W,"00")&amp;" ("&amp;TEXT(_xlpm.S,"d/m")&amp;" - "&amp;TEXT(_xlpm.E,"d/m")&amp;")"
 ))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0A00-000004000000}" name="COMPANY" dataDxfId="90"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0A00-000005000000}" name="CATEGORY" dataDxfId="89"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0A00-000006000000}" name="MANDAY" dataDxfId="88"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0A00-000007000000}" name="MANHOUR" dataDxfId="87"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0A00-000004000000}" name="COMPANY" dataDxfId="106"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0A00-000005000000}" name="CATEGORY" dataDxfId="105"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0A00-000006000000}" name="MANDAY" dataDxfId="104"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0A00-000007000000}" name="MANHOUR" dataDxfId="103"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{00000000-000C-0000-FFFF-FFFF0B000000}" name="ANTARAKOH" displayName="ANTARAKOH" ref="A5:G68" totalsRowShown="0" headerRowDxfId="86" dataDxfId="84" headerRowBorderDxfId="85" tableBorderDxfId="83">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{00000000-000C-0000-FFFF-FFFF0B000000}" name="ANTARAKOH" displayName="ANTARAKOH" ref="A5:G68" totalsRowShown="0" headerRowDxfId="102" dataDxfId="100" headerRowBorderDxfId="101" tableBorderDxfId="99">
   <autoFilter ref="A5:G68" xr:uid="{00000000-0009-0000-0100-00000C000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0B00-000001000000}" name="DATE" dataDxfId="82"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0B00-000002000000}" name="DAY" dataDxfId="81">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0B00-000001000000}" name="DATE" dataDxfId="98"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0B00-000002000000}" name="DAY" dataDxfId="97">
       <calculatedColumnFormula>A6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0B00-000003000000}" name="WEEK" dataDxfId="80"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0B00-000004000000}" name="COMPANY" dataDxfId="79"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0B00-000005000000}" name="CATEGORY" dataDxfId="78"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0B00-000006000000}" name="MANDAY" dataDxfId="77"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0B00-000007000000}" name="MANHOUR" dataDxfId="76"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0B00-000003000000}" name="WEEK" dataDxfId="96"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0B00-000004000000}" name="COMPANY" dataDxfId="95"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0B00-000005000000}" name="CATEGORY" dataDxfId="94"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0B00-000006000000}" name="MANDAY" dataDxfId="93"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0B00-000007000000}" name="MANHOUR" dataDxfId="92"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{00000000-000C-0000-FFFF-FFFF0C000000}" name="SECURITYBOAT" displayName="SECURITYBOAT" ref="A5:G68" totalsRowShown="0" headerRowDxfId="75" dataDxfId="73" headerRowBorderDxfId="74" tableBorderDxfId="72">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{00000000-000C-0000-FFFF-FFFF0C000000}" name="SECURITYBOAT" displayName="SECURITYBOAT" ref="A5:G68" totalsRowShown="0" headerRowDxfId="91" dataDxfId="89" headerRowBorderDxfId="90" tableBorderDxfId="88">
   <autoFilter ref="A5:G68" xr:uid="{00000000-0009-0000-0100-00000D000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0C00-000001000000}" name="DATE" dataDxfId="71"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0C00-000002000000}" name="DAY" dataDxfId="70">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0C00-000001000000}" name="DATE" dataDxfId="87"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0C00-000002000000}" name="DAY" dataDxfId="86">
       <calculatedColumnFormula>A6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0C00-000003000000}" name="WEEK" dataDxfId="69">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0C00-000003000000}" name="WEEK" dataDxfId="85">
       <calculatedColumnFormula>IF(SECURITYBOAT[[#This Row],[DATE]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((SECURITYBOAT[[#This Row],[DATE]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -7882,24 +7945,24 @@
 "W"&amp;TEXT(_xlpm.W,"00")&amp;" ("&amp;TEXT(_xlpm.S,"d/m")&amp;" - "&amp;TEXT(_xlpm.E,"d/m")&amp;")"
 ))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0C00-000004000000}" name="COMPANY" dataDxfId="68"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0C00-000005000000}" name="CATEGORY" dataDxfId="67"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0C00-000006000000}" name="MANDAY" dataDxfId="66"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0C00-000007000000}" name="MANHOUR" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0C00-000004000000}" name="COMPANY" dataDxfId="84"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0C00-000005000000}" name="CATEGORY" dataDxfId="83"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0C00-000006000000}" name="MANDAY" dataDxfId="82"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0C00-000007000000}" name="MANHOUR" dataDxfId="81"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{00000000-000C-0000-FFFF-FFFF0D000000}" name="PASSENGER_BOAT" displayName="PASSENGER_BOAT" ref="A5:G68" totalsRowShown="0" headerRowDxfId="64" dataDxfId="62" headerRowBorderDxfId="63" tableBorderDxfId="61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{00000000-000C-0000-FFFF-FFFF0D000000}" name="PASSENGER_BOAT" displayName="PASSENGER_BOAT" ref="A5:G68" totalsRowShown="0" headerRowDxfId="80" dataDxfId="78" headerRowBorderDxfId="79" tableBorderDxfId="77">
   <autoFilter ref="A5:G68" xr:uid="{00000000-0009-0000-0100-00000E000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0D00-000001000000}" name="DATE" dataDxfId="60"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0D00-000002000000}" name="DAY" dataDxfId="59">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0D00-000001000000}" name="DATE" dataDxfId="76"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0D00-000002000000}" name="DAY" dataDxfId="75">
       <calculatedColumnFormula>A6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0D00-000003000000}" name="WEEK" dataDxfId="58">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0D00-000003000000}" name="WEEK" dataDxfId="74">
       <calculatedColumnFormula>IF(PASSENGER_BOAT[[#This Row],[DATE]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((PASSENGER_BOAT[[#This Row],[DATE]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -7907,24 +7970,24 @@
 "W"&amp;TEXT(_xlpm.W,"00")&amp;" ("&amp;TEXT(_xlpm.S,"d/m")&amp;" - "&amp;TEXT(_xlpm.E,"d/m")&amp;")"
 ))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0D00-000004000000}" name="COMPANY" dataDxfId="57"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0D00-000005000000}" name="CATEGORY" dataDxfId="56"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0D00-000006000000}" name="MANDAY" dataDxfId="55"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0D00-000007000000}" name="MANHOUR" dataDxfId="54"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0D00-000004000000}" name="COMPANY" dataDxfId="73"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0D00-000005000000}" name="CATEGORY" dataDxfId="72"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0D00-000006000000}" name="MANDAY" dataDxfId="71"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0D00-000007000000}" name="MANHOUR" dataDxfId="70"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF0E000000}" name="Lagging" displayName="Lagging" ref="A5:N178" totalsRowShown="0" headerRowDxfId="53" dataDxfId="51" headerRowBorderDxfId="52" tableBorderDxfId="50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{00000000-000C-0000-FFFF-FFFF0E000000}" name="Lagging" displayName="Lagging" ref="A5:N178" totalsRowShown="0" headerRowDxfId="69" dataDxfId="67" headerRowBorderDxfId="68" tableBorderDxfId="66">
   <autoFilter ref="A5:N178" xr:uid="{00000000-0009-0000-0100-00000F000000}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0E00-000001000000}" name="DATE" dataDxfId="49"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0E00-000002000000}" name="DAY" dataDxfId="48">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0E00-000001000000}" name="DATE" dataDxfId="65"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0E00-000002000000}" name="DAY" dataDxfId="64">
       <calculatedColumnFormula>A6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0E00-000003000000}" name="WEEK" dataDxfId="47">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0E00-000003000000}" name="WEEK" dataDxfId="63">
       <calculatedColumnFormula>IF(Lagging[[#This Row],[DATE]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Lagging[[#This Row],[DATE]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -7932,31 +7995,31 @@
 "W"&amp;TEXT(_xlpm.W,"00")&amp;" ("&amp;TEXT(_xlpm.S,"d/m")&amp;" - "&amp;TEXT(_xlpm.E,"d/m")&amp;")"
 ))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0E00-000006000000}" name="FATALITY" dataDxfId="46"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0E00-000007000000}" name="LTI" dataDxfId="45"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0E00-000004000000}" name="RWC" dataDxfId="44"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0E00-000005000000}" name="MTC" dataDxfId="43"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0E00-000008000000}" name="FAC" dataDxfId="42"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0E00-000009000000}" name="DANGEROUS OCCURANCE" dataDxfId="41"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0E00-00000A000000}" name="PROPERTY DAMAGE" dataDxfId="40"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0E00-00000B000000}" name="NEAR MISS" dataDxfId="39"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0E00-00000C000000}" name="FIRE INCIDENT" dataDxfId="38"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0E00-00000D000000}" name="REGULATORY NON COMPLIANCE" dataDxfId="37"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0E00-00000E000000}" name="LoPC" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0E00-000006000000}" name="FATALITY" dataDxfId="62"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0E00-000007000000}" name="LTI" dataDxfId="61"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0E00-000004000000}" name="RWC" dataDxfId="60"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0E00-000005000000}" name="MTC" dataDxfId="59"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0E00-000008000000}" name="FAC" dataDxfId="58"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0E00-000009000000}" name="DANGEROUS OCCURANCE" dataDxfId="57"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0E00-00000A000000}" name="PROPERTY DAMAGE" dataDxfId="56"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0E00-00000B000000}" name="NEAR MISS" dataDxfId="55"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0E00-00000C000000}" name="FIRE INCIDENT" dataDxfId="54"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0E00-00000D000000}" name="REGULATORY NON COMPLIANCE" dataDxfId="53"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0E00-00000E000000}" name="LoPC" dataDxfId="52"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{00000000-000C-0000-FFFF-FFFF0F000000}" name="Leading" displayName="Leading" ref="A5:O178" totalsRowShown="0" headerRowDxfId="35" dataDxfId="33" headerRowBorderDxfId="34" tableBorderDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{00000000-000C-0000-FFFF-FFFF0F000000}" name="Leading" displayName="Leading" ref="A5:O178" totalsRowShown="0" headerRowDxfId="51" dataDxfId="49" headerRowBorderDxfId="50" tableBorderDxfId="48">
   <autoFilter ref="A5:O178" xr:uid="{00000000-0009-0000-0100-000010000000}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0F00-000001000000}" name="DATE" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0F00-000002000000}" name="DAY" dataDxfId="30">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0F00-000001000000}" name="DATE" dataDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0F00-000002000000}" name="DAY" dataDxfId="46">
       <calculatedColumnFormula>A6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0F00-000003000000}" name="WEEK" dataDxfId="29">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0F00-000003000000}" name="WEEK" dataDxfId="45">
       <calculatedColumnFormula>IF(Leading[[#This Row],[DATE]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Leading[[#This Row],[DATE]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -7964,42 +8027,36 @@
 "W"&amp;TEXT(_xlpm.W,"00")&amp;" ("&amp;TEXT(_xlpm.S,"d/m")&amp;" - "&amp;TEXT(_xlpm.E,"d/m")&amp;")"
 ))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0F00-000006000000}" name="HSE INDUCTION" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0F00-000007000000}" name="TOOLBOX MEETING" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0F00-000004000000}" name="HSE COORDINATION MEETING" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0F00-000005000000}" name="HSE COMMITTEE MEETING" dataDxfId="25"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0F00-000008000000}" name="EMERGENCY DRILL" dataDxfId="24"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0F00-00000F000000}" name="WORKPLACE INSPECTION" dataDxfId="23"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0F00-000010000000}" name="HSE WALKABOUT" dataDxfId="22"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0F00-000011000000}" name="WEEKLY HOUSEKEEPING" dataDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0F00-000009000000}" name="BESAFE CARD" dataDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0F00-00000A000000}" name="HSE CAMPAIGN" dataDxfId="19"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0F00-00000B000000}" name="REWARDS &amp; RECOGNITION" dataDxfId="18"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0F00-00000C000000}" name="CONSEQUENCE MANAGEMENT" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0F00-000006000000}" name="HSE INDUCTION" dataDxfId="44"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0F00-000007000000}" name="TOOLBOX MEETING" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0F00-000004000000}" name="HSE COORDINATION MEETING" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0F00-000005000000}" name="HSE COMMITTEE MEETING" dataDxfId="41"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0F00-000008000000}" name="EMERGENCY DRILL" dataDxfId="40"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0F00-00000F000000}" name="WORKPLACE INSPECTION" dataDxfId="39"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0F00-000010000000}" name="HSE WALKABOUT" dataDxfId="38"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0F00-000011000000}" name="WEEKLY HOUSEKEEPING" dataDxfId="37"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0F00-000009000000}" name="BESAFE CARD" dataDxfId="36"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0F00-00000A000000}" name="HSE CAMPAIGN" dataDxfId="35"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0F00-00000B000000}" name="REWARDS &amp; RECOGNITION" dataDxfId="34"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0F00-00000C000000}" name="CONSEQUENCE MANAGEMENT" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{00000000-000C-0000-FFFF-FFFF10000000}" name="Table3" displayName="Table3" ref="A1:M170" totalsRowShown="0" headerRowDxfId="223" dataDxfId="222" tableBorderDxfId="221">
-  <autoFilter ref="A1:M170" xr:uid="{00000000-0009-0000-0100-000011000000}">
-    <filterColumn colId="5">
-      <filters>
-        <dateGroupItem year="2026" month="9" dateTimeGrouping="month"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{00000000-000C-0000-FFFF-FFFF10000000}" name="Table3" displayName="Table3" ref="A1:M174" totalsRowShown="0" headerRowDxfId="32" dataDxfId="31" tableBorderDxfId="30">
+  <autoFilter ref="A1:M174" xr:uid="{00000000-0009-0000-0100-000011000000}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1000-000001000000}" name="No" dataDxfId="220"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1000-000002000000}" name="BSC No" dataDxfId="219"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1000-000003000000}" name="BSC Type" dataDxfId="218"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1000-000004000000}" name="Hazard Type RAW" dataDxfId="217"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-1000-00000A000000}" name="Hazard Type" dataDxfId="216">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-1000-000001000000}" name="No" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-1000-000002000000}" name="BSC No" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-1000-000003000000}" name="BSC Type" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-1000-000004000000}" name="Hazard Type RAW" dataDxfId="26"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-1000-00000A000000}" name="Hazard Type" dataDxfId="25">
       <calculatedColumnFormula>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1000-000005000000}" name="Date Reported" dataDxfId="215"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-1000-00000B000000}" name="Week" dataDxfId="214" dataCellStyle="Normal 2">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-1000-000005000000}" name="Date Reported" dataDxfId="24"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-1000-00000B000000}" name="Week" dataDxfId="23" dataCellStyle="Normal 2">
       <calculatedColumnFormula>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -8007,12 +8064,12 @@
 "W"&amp;TEXT(_xlpm.W,"00")&amp;" ("&amp;TEXT(_xlpm.S,"d/m")&amp;" - "&amp;TEXT(_xlpm.E,"d/m")&amp;")"
 ))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1000-000006000000}" name="Date Observed" dataDxfId="213"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-1000-000007000000}" name="Observed By" dataDxfId="212"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-1000-00000C000000}" name="Company" dataDxfId="211" dataCellStyle="Normal 2"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-1000-00000D000000}" name="Position" dataDxfId="210" dataCellStyle="Normal 2"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-1000-000008000000}" name="What and where hazard/act observed and_x000a_discussed with worker/supervisor/manager?" dataDxfId="209"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-1000-000009000000}" name="Status" dataDxfId="208"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-1000-000006000000}" name="Date Observed" dataDxfId="22"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-1000-000007000000}" name="Observed By" dataDxfId="21"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-1000-00000C000000}" name="Company" dataDxfId="20" dataCellStyle="Normal 2"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-1000-00000D000000}" name="Position" dataDxfId="19" dataCellStyle="Normal 2"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-1000-000008000000}" name="What and where hazard/act observed and_x000a_discussed with worker/supervisor/manager?" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-1000-000009000000}" name="Status" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8049,50 +8106,50 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="POM_SITE" displayName="POM_SITE" ref="A5:G178" totalsRowShown="0" headerRowDxfId="196" dataDxfId="194" headerRowBorderDxfId="195" tableBorderDxfId="193">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="POM_SITE" displayName="POM_SITE" ref="A5:G178" totalsRowShown="0" headerRowDxfId="212" dataDxfId="210" headerRowBorderDxfId="211" tableBorderDxfId="209">
   <autoFilter ref="A5:G178" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="DATE" dataDxfId="192"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="DAY" dataDxfId="191">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="DATE" dataDxfId="208"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="DAY" dataDxfId="207">
       <calculatedColumnFormula>A6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="WEEK" dataDxfId="190"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="COMPANY" dataDxfId="189"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="CATEGORY" dataDxfId="188"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="MANDAY" dataDxfId="187"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="MANHOUR" dataDxfId="186"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="WEEK" dataDxfId="206"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="COMPANY" dataDxfId="205"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="CATEGORY" dataDxfId="204"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="MANDAY" dataDxfId="203"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="MANHOUR" dataDxfId="202"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="POC" displayName="POC" ref="A5:G178" totalsRowShown="0" headerRowDxfId="185" dataDxfId="183" headerRowBorderDxfId="184" tableBorderDxfId="182">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="POC" displayName="POC" ref="A5:G178" totalsRowShown="0" headerRowDxfId="201" dataDxfId="199" headerRowBorderDxfId="200" tableBorderDxfId="198">
   <autoFilter ref="A5:G178" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="DATE" dataDxfId="181"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="DAY" dataDxfId="180">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="DATE" dataDxfId="197"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="DAY" dataDxfId="196">
       <calculatedColumnFormula>A6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="WEEK" dataDxfId="179"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="COMPANY" dataDxfId="178"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="CATEGORY" dataDxfId="177"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="MANDAY" dataDxfId="176"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="MANHOUR" dataDxfId="175"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="WEEK" dataDxfId="195"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="COMPANY" dataDxfId="194"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="CATEGORY" dataDxfId="193"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="MANDAY" dataDxfId="192"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="MANHOUR" dataDxfId="191"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="GEOMETRA" displayName="GEOMETRA" ref="A5:G9" totalsRowShown="0" headerRowDxfId="174" dataDxfId="172" headerRowBorderDxfId="173" tableBorderDxfId="171">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="GEOMETRA" displayName="GEOMETRA" ref="A5:G9" totalsRowShown="0" headerRowDxfId="190" dataDxfId="188" headerRowBorderDxfId="189" tableBorderDxfId="187">
   <autoFilter ref="A5:G9" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="DATE" dataDxfId="170"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="DAY" dataDxfId="169">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="DATE" dataDxfId="186"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="DAY" dataDxfId="185">
       <calculatedColumnFormula>A6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="WEEK" dataDxfId="168">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="WEEK" dataDxfId="184">
       <calculatedColumnFormula>IF(GEOMETRA[[#This Row],[DATE]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((GEOMETRA[[#This Row],[DATE]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -8100,42 +8157,42 @@
 "W"&amp;TEXT(_xlpm.W,"00")&amp;" ("&amp;TEXT(_xlpm.S,"d/m")&amp;" - "&amp;TEXT(_xlpm.E,"d/m")&amp;")"
 ))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="COMPANY" dataDxfId="167"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="CATEGORY" dataDxfId="166"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="MANDAY" dataDxfId="165"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="MANHOUR" dataDxfId="164"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="COMPANY" dataDxfId="183"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="CATEGORY" dataDxfId="182"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="MANDAY" dataDxfId="181"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="MANHOUR" dataDxfId="180"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="KROTARY" displayName="KROTARY" ref="A5:G131" totalsRowShown="0" headerRowDxfId="163" dataDxfId="161" headerRowBorderDxfId="162" tableBorderDxfId="160">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="KROTARY" displayName="KROTARY" ref="A5:G131" totalsRowShown="0" headerRowDxfId="179" dataDxfId="177" headerRowBorderDxfId="178" tableBorderDxfId="176">
   <autoFilter ref="A5:G131" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="DATE" dataDxfId="159"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="DAY" dataDxfId="158">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="DATE" dataDxfId="175"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="DAY" dataDxfId="174">
       <calculatedColumnFormula>A6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="WEEK" dataDxfId="157"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="COMPANY" dataDxfId="156"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="CATEGORY" dataDxfId="155"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="MANDAY" dataDxfId="154"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="MANHOUR" dataDxfId="153"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="WEEK" dataDxfId="173"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="COMPANY" dataDxfId="172"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="CATEGORY" dataDxfId="171"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="MANDAY" dataDxfId="170"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="MANHOUR" dataDxfId="169"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="STARWORK" displayName="STARWORK" ref="A5:G68" totalsRowShown="0" headerRowDxfId="152" dataDxfId="150" headerRowBorderDxfId="151" tableBorderDxfId="149">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="STARWORK" displayName="STARWORK" ref="A5:G68" totalsRowShown="0" headerRowDxfId="168" dataDxfId="166" headerRowBorderDxfId="167" tableBorderDxfId="165">
   <autoFilter ref="A5:G68" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="DATE" dataDxfId="148"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="DAY" dataDxfId="147">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="DATE" dataDxfId="164"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="DAY" dataDxfId="163">
       <calculatedColumnFormula>A6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="WEEK" dataDxfId="146">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="WEEK" dataDxfId="162">
       <calculatedColumnFormula>IF(STARWORK[[#This Row],[DATE]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((STARWORK[[#This Row],[DATE]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -8143,24 +8200,24 @@
 "W"&amp;TEXT(_xlpm.W,"00")&amp;" ("&amp;TEXT(_xlpm.S,"d/m")&amp;" - "&amp;TEXT(_xlpm.E,"d/m")&amp;")"
 ))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="COMPANY" dataDxfId="145"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="CATEGORY" dataDxfId="144"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="MANDAY" dataDxfId="143"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="MANHOUR" dataDxfId="142"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="COMPANY" dataDxfId="161"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="CATEGORY" dataDxfId="160"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="MANDAY" dataDxfId="159"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="MANHOUR" dataDxfId="158"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="MILLENIUM" displayName="MILLENIUM" ref="A5:G7" totalsRowShown="0" headerRowDxfId="141" dataDxfId="139" headerRowBorderDxfId="140" tableBorderDxfId="138">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="MILLENIUM" displayName="MILLENIUM" ref="A5:G7" totalsRowShown="0" headerRowDxfId="157" dataDxfId="155" headerRowBorderDxfId="156" tableBorderDxfId="154">
   <autoFilter ref="A5:G7" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="DATE" dataDxfId="137"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="DAY" dataDxfId="136">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="DATE" dataDxfId="153"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="DAY" dataDxfId="152">
       <calculatedColumnFormula>A6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="WEEK" dataDxfId="135">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="WEEK" dataDxfId="151">
       <calculatedColumnFormula>IF(MILLENIUM[[#This Row],[DATE]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((MILLENIUM[[#This Row],[DATE]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -8168,48 +8225,48 @@
 "W"&amp;TEXT(_xlpm.W,"00")&amp;" ("&amp;TEXT(_xlpm.S,"d/m")&amp;" - "&amp;TEXT(_xlpm.E,"d/m")&amp;")"
 ))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="COMPANY" dataDxfId="134"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="CATEGORY" dataDxfId="133"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="MANDAY" dataDxfId="132"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="MANHOUR" dataDxfId="131"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="COMPANY" dataDxfId="150"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="CATEGORY" dataDxfId="149"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="MANDAY" dataDxfId="148"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="MANHOUR" dataDxfId="147"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="GEOLAB" displayName="GEOLAB" ref="A5:G55" totalsRowShown="0" headerRowDxfId="130" dataDxfId="128" headerRowBorderDxfId="129" tableBorderDxfId="127">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="GEOLAB" displayName="GEOLAB" ref="A5:G55" totalsRowShown="0" headerRowDxfId="146" dataDxfId="144" headerRowBorderDxfId="145" tableBorderDxfId="143">
   <autoFilter ref="A5:G55" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="DATE" dataDxfId="126"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="DAY" dataDxfId="125">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="DATE" dataDxfId="142"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="DAY" dataDxfId="141">
       <calculatedColumnFormula>A6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="WEEK" dataDxfId="124">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="WEEK" dataDxfId="140">
       <calculatedColumnFormula>IF(GEOLAB[[#This Row],[DATE]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((GEOLAB[[#This Row],[DATE]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,_xlpm.E,_xlpm.S+6,
 "W"&amp;TEXT(_xlpm.W,"00")&amp;" ("&amp;TEXT(_xlpm.S,"d/m")&amp;" - "&amp;TEXT(_xlpm.E,"d/m")&amp;")"
 ))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="COMPANY" dataDxfId="123"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="CATEGORY" dataDxfId="122"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="MANDAY" dataDxfId="121"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="MANHOUR" dataDxfId="120"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="COMPANY" dataDxfId="139"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="CATEGORY" dataDxfId="138"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="MANDAY" dataDxfId="137"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="MANHOUR" dataDxfId="136"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="TWINSTEEL" displayName="TWINSTEEL" ref="A5:G90" totalsRowShown="0" headerRowDxfId="119" dataDxfId="117" headerRowBorderDxfId="118" tableBorderDxfId="116">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="TWINSTEEL" displayName="TWINSTEEL" ref="A5:G90" totalsRowShown="0" headerRowDxfId="135" dataDxfId="133" headerRowBorderDxfId="134" tableBorderDxfId="132">
   <autoFilter ref="A5:G90" xr:uid="{00000000-0009-0000-0100-000009000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="DATE" dataDxfId="115"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="DAY" dataDxfId="114">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="DATE" dataDxfId="131"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="DAY" dataDxfId="130">
       <calculatedColumnFormula>A6</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="WEEK" dataDxfId="113">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="WEEK" dataDxfId="129">
       <calculatedColumnFormula>IF(TWINSTEEL[[#This Row],[DATE]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
 _xlpm.W,INT((TWINSTEEL[[#This Row],[DATE]]-DATE(2026,4,11))/7)+1,
 _xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
@@ -8217,10 +8274,10 @@
 "W"&amp;TEXT(_xlpm.W,"00")&amp;" ("&amp;TEXT(_xlpm.S,"d/m")&amp;" - "&amp;TEXT(_xlpm.E,"d/m")&amp;")"
 ))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="COMPANY" dataDxfId="112"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="CATEGORY" dataDxfId="111"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="MANDAY" dataDxfId="110"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="MANHOUR" dataDxfId="109"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="COMPANY" dataDxfId="128"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="CATEGORY" dataDxfId="127"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="MANDAY" dataDxfId="126"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="MANHOUR" dataDxfId="125"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -41326,7 +41383,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
-  <dimension ref="A1:M170"/>
+  <dimension ref="A1:M174"/>
   <sheetFormatPr defaultRowHeight="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="15" customWidth="1"/>
@@ -41382,7 +41439,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16">
         <v>1</v>
       </c>
@@ -41430,7 +41487,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16">
         <v>2</v>
       </c>
@@ -41478,7 +41535,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16">
         <v>3</v>
       </c>
@@ -41526,7 +41583,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16">
         <v>4</v>
       </c>
@@ -41574,7 +41631,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16">
         <v>5</v>
       </c>
@@ -41622,7 +41679,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16">
         <v>6</v>
       </c>
@@ -41670,7 +41727,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
         <v>7</v>
       </c>
@@ -41718,7 +41775,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16">
         <v>8</v>
       </c>
@@ -41766,7 +41823,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16">
         <v>9</v>
       </c>
@@ -41814,7 +41871,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16">
         <v>10</v>
       </c>
@@ -41862,7 +41919,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16">
         <v>11</v>
       </c>
@@ -41910,7 +41967,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16">
         <v>12</v>
       </c>
@@ -41958,7 +42015,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16">
         <v>13</v>
       </c>
@@ -42006,7 +42063,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16">
         <v>14</v>
       </c>
@@ -42054,7 +42111,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16">
         <v>15</v>
       </c>
@@ -42102,7 +42159,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16">
         <v>16</v>
       </c>
@@ -42150,7 +42207,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16">
         <v>17</v>
       </c>
@@ -42198,7 +42255,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16">
         <v>18</v>
       </c>
@@ -42246,7 +42303,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16">
         <v>19</v>
       </c>
@@ -42294,7 +42351,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16">
         <v>20</v>
       </c>
@@ -42342,7 +42399,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16">
         <v>21</v>
       </c>
@@ -42390,7 +42447,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16">
         <v>22</v>
       </c>
@@ -42438,7 +42495,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16">
         <v>23</v>
       </c>
@@ -42486,7 +42543,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16">
         <v>24</v>
       </c>
@@ -42534,7 +42591,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16">
         <v>25</v>
       </c>
@@ -42582,7 +42639,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16">
         <v>26</v>
       </c>
@@ -42630,7 +42687,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16">
         <v>27</v>
       </c>
@@ -42678,7 +42735,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16">
         <v>28</v>
       </c>
@@ -42726,7 +42783,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16">
         <v>29</v>
       </c>
@@ -42774,7 +42831,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16">
         <v>30</v>
       </c>
@@ -42822,7 +42879,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="16">
         <v>31</v>
       </c>
@@ -42870,7 +42927,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16">
         <v>32</v>
       </c>
@@ -42918,7 +42975,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
         <v>33</v>
       </c>
@@ -42966,7 +43023,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="16">
         <v>34</v>
       </c>
@@ -43014,7 +43071,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16">
         <v>35</v>
       </c>
@@ -43062,7 +43119,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="16">
         <v>36</v>
       </c>
@@ -43110,7 +43167,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="16">
         <v>37</v>
       </c>
@@ -43158,7 +43215,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="16">
         <v>38</v>
       </c>
@@ -43206,7 +43263,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="16">
         <v>39</v>
       </c>
@@ -43254,7 +43311,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="16">
         <v>40</v>
       </c>
@@ -43302,7 +43359,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="16">
         <v>41</v>
       </c>
@@ -43350,7 +43407,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="16">
         <v>42</v>
       </c>
@@ -48203,20 +48260,20 @@
         <v>143</v>
       </c>
       <c r="B144" s="43" t="s">
-        <v>428</v>
+        <v>522</v>
       </c>
       <c r="C144" s="44" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="D144" s="44" t="s">
-        <v>429</v>
+        <v>526</v>
       </c>
       <c r="E144" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
-        <v>Inadequate or Improper Protective</v>
+        <v>Defective Tools, Equipment or Mat</v>
       </c>
       <c r="F144" s="45">
-        <v>46294</v>
+        <v>46291</v>
       </c>
       <c r="G144" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
@@ -48228,19 +48285,19 @@
         <v>W25 (26/9 - 2/10)</v>
       </c>
       <c r="H144" s="45">
-        <v>46294</v>
+        <v>46291</v>
       </c>
       <c r="I144" s="47" t="s">
-        <v>111</v>
-      </c>
-      <c r="J144" s="44" t="s">
-        <v>82</v>
+        <v>527</v>
+      </c>
+      <c r="J144" s="54" t="s">
+        <v>72</v>
       </c>
       <c r="K144" s="44" t="s">
         <v>73</v>
       </c>
       <c r="L144" s="48" t="s">
-        <v>430</v>
+        <v>528</v>
       </c>
       <c r="M144" s="49" t="s">
         <v>187</v>
@@ -48251,20 +48308,20 @@
         <v>144</v>
       </c>
       <c r="B145" s="43" t="s">
-        <v>431</v>
+        <v>523</v>
       </c>
       <c r="C145" s="44" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D145" s="44" t="s">
         <v>70</v>
       </c>
       <c r="E145" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
-        <v>Good Catch</v>
+        <v>Suggestion for Improvement</v>
       </c>
       <c r="F145" s="45">
-        <v>46294</v>
+        <v>46291</v>
       </c>
       <c r="G145" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
@@ -48276,19 +48333,19 @@
         <v>W25 (26/9 - 2/10)</v>
       </c>
       <c r="H145" s="45">
-        <v>46294</v>
+        <v>46291</v>
       </c>
       <c r="I145" s="47" t="s">
-        <v>111</v>
-      </c>
-      <c r="J145" s="44" t="s">
-        <v>82</v>
+        <v>527</v>
+      </c>
+      <c r="J145" s="55" t="s">
+        <v>72</v>
       </c>
       <c r="K145" s="44" t="s">
         <v>73</v>
       </c>
       <c r="L145" s="48" t="s">
-        <v>432</v>
+        <v>529</v>
       </c>
       <c r="M145" s="49" t="s">
         <v>187</v>
@@ -48299,20 +48356,20 @@
         <v>145</v>
       </c>
       <c r="B146" s="43" t="s">
-        <v>433</v>
+        <v>524</v>
       </c>
       <c r="C146" s="44" t="s">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="D146" s="44" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="E146" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
-        <v>Others - Hazardous Environmental Condition</v>
+        <v>Safe Condition</v>
       </c>
       <c r="F146" s="45">
-        <v>46294</v>
+        <v>46291</v>
       </c>
       <c r="G146" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
@@ -48324,43 +48381,43 @@
         <v>W25 (26/9 - 2/10)</v>
       </c>
       <c r="H146" s="45">
-        <v>46294</v>
+        <v>46291</v>
       </c>
       <c r="I146" s="47" t="s">
-        <v>81</v>
-      </c>
-      <c r="J146" s="44" t="s">
+        <v>192</v>
+      </c>
+      <c r="J146" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="K146" s="44" t="s">
-        <v>73</v>
+      <c r="K146" s="55" t="s">
+        <v>193</v>
       </c>
       <c r="L146" s="48" t="s">
-        <v>434</v>
+        <v>530</v>
       </c>
       <c r="M146" s="49" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="147" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="43">
         <v>146</v>
       </c>
       <c r="B147" s="43" t="s">
-        <v>435</v>
+        <v>525</v>
       </c>
       <c r="C147" s="44" t="s">
-        <v>116</v>
+        <v>69</v>
       </c>
       <c r="D147" s="44" t="s">
-        <v>429</v>
+        <v>70</v>
       </c>
       <c r="E147" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
-        <v>Inadequate or Improper Protective</v>
+        <v>Suggestion for Improvement</v>
       </c>
       <c r="F147" s="45">
-        <v>46296</v>
+        <v>46291</v>
       </c>
       <c r="G147" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
@@ -48372,43 +48429,43 @@
         <v>W25 (26/9 - 2/10)</v>
       </c>
       <c r="H147" s="45">
-        <v>46296</v>
+        <v>46292</v>
       </c>
       <c r="I147" s="47" t="s">
-        <v>436</v>
-      </c>
-      <c r="J147" s="44" t="s">
-        <v>72</v>
-      </c>
-      <c r="K147" s="44" t="s">
-        <v>73</v>
+        <v>331</v>
+      </c>
+      <c r="J147" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="K147" s="55" t="s">
+        <v>193</v>
       </c>
       <c r="L147" s="48" t="s">
-        <v>437</v>
+        <v>531</v>
       </c>
       <c r="M147" s="49" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="148" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="43">
         <v>147</v>
       </c>
       <c r="B148" s="43" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="C148" s="44" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="D148" s="44" t="s">
-        <v>89</v>
+        <v>429</v>
       </c>
       <c r="E148" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
-        <v>Inadequate Warning System</v>
+        <v>Inadequate or Improper Protective</v>
       </c>
       <c r="F148" s="45">
-        <v>46296</v>
+        <v>46294</v>
       </c>
       <c r="G148" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
@@ -48420,43 +48477,43 @@
         <v>W25 (26/9 - 2/10)</v>
       </c>
       <c r="H148" s="45">
-        <v>46296</v>
+        <v>46294</v>
       </c>
       <c r="I148" s="47" t="s">
-        <v>199</v>
-      </c>
-      <c r="J148" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="J148" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="K148" s="44" t="s">
-        <v>193</v>
+      <c r="K148" s="55" t="s">
+        <v>73</v>
       </c>
       <c r="L148" s="48" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="M148" s="49" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="149" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="43">
         <v>148</v>
       </c>
       <c r="B149" s="43" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="C149" s="44" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D149" s="44" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="E149" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
-        <v>Inadequate Warning System</v>
+        <v>Good Catch</v>
       </c>
       <c r="F149" s="45">
-        <v>46296</v>
+        <v>46294</v>
       </c>
       <c r="G149" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
@@ -48468,43 +48525,43 @@
         <v>W25 (26/9 - 2/10)</v>
       </c>
       <c r="H149" s="45">
-        <v>46296</v>
+        <v>46294</v>
       </c>
       <c r="I149" s="47" t="s">
-        <v>199</v>
-      </c>
-      <c r="J149" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="J149" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="K149" s="44" t="s">
-        <v>193</v>
+      <c r="K149" s="55" t="s">
+        <v>73</v>
       </c>
       <c r="L149" s="48" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="M149" s="49" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="150" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="43">
         <v>149</v>
       </c>
       <c r="B150" s="43" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="C150" s="44" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="D150" s="44" t="s">
-        <v>429</v>
+        <v>117</v>
       </c>
       <c r="E150" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
-        <v>Inadequate or Improper Protective</v>
+        <v>Others - Hazardous Environmental Condition</v>
       </c>
       <c r="F150" s="45">
-        <v>46296</v>
+        <v>46294</v>
       </c>
       <c r="G150" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
@@ -48516,30 +48573,30 @@
         <v>W25 (26/9 - 2/10)</v>
       </c>
       <c r="H150" s="45">
-        <v>46296</v>
+        <v>46294</v>
       </c>
       <c r="I150" s="47" t="s">
-        <v>199</v>
-      </c>
-      <c r="J150" s="44" t="s">
+        <v>81</v>
+      </c>
+      <c r="J150" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="K150" s="44" t="s">
-        <v>193</v>
+      <c r="K150" s="55" t="s">
+        <v>73</v>
       </c>
       <c r="L150" s="48" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="M150" s="49" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="151" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="43">
         <v>150</v>
       </c>
       <c r="B151" s="43" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="C151" s="44" t="s">
         <v>116</v>
@@ -48567,40 +48624,40 @@
         <v>46296</v>
       </c>
       <c r="I151" s="47" t="s">
-        <v>230</v>
-      </c>
-      <c r="J151" s="44" t="s">
-        <v>82</v>
-      </c>
-      <c r="K151" s="44" t="s">
-        <v>193</v>
+        <v>436</v>
+      </c>
+      <c r="J151" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="K151" s="55" t="s">
+        <v>73</v>
       </c>
       <c r="L151" s="48" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="M151" s="49" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="152" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="43">
         <v>151</v>
       </c>
       <c r="B152" s="43" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="C152" s="44" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="D152" s="44" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="E152" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
-        <v>Safe Condition</v>
+        <v>Inadequate Warning System</v>
       </c>
       <c r="F152" s="45">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="G152" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
@@ -48612,43 +48669,43 @@
         <v>W25 (26/9 - 2/10)</v>
       </c>
       <c r="H152" s="45">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="I152" s="47" t="s">
-        <v>237</v>
-      </c>
-      <c r="J152" s="44" t="s">
-        <v>168</v>
-      </c>
-      <c r="K152" s="44" t="s">
-        <v>175</v>
+        <v>199</v>
+      </c>
+      <c r="J152" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="K152" s="55" t="s">
+        <v>193</v>
       </c>
       <c r="L152" s="48" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="M152" s="49" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="153" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="43">
         <v>152</v>
       </c>
       <c r="B153" s="43" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="C153" s="44" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="D153" s="44" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="E153" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
-        <v>Safe Condition</v>
+        <v>Inadequate Warning System</v>
       </c>
       <c r="F153" s="45">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="G153" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
@@ -48660,43 +48717,43 @@
         <v>W25 (26/9 - 2/10)</v>
       </c>
       <c r="H153" s="45">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="I153" s="47" t="s">
-        <v>331</v>
-      </c>
-      <c r="J153" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="K153" s="44" t="s">
+        <v>199</v>
+      </c>
+      <c r="J153" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="K153" s="55" t="s">
         <v>193</v>
       </c>
       <c r="L153" s="48" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="M153" s="49" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="154" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="43">
         <v>153</v>
       </c>
       <c r="B154" s="43" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="C154" s="44" t="s">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="D154" s="44" t="s">
-        <v>70</v>
+        <v>429</v>
       </c>
       <c r="E154" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
-        <v>Safe Condition</v>
+        <v>Inadequate or Improper Protective</v>
       </c>
       <c r="F154" s="45">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="G154" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
@@ -48708,30 +48765,30 @@
         <v>W25 (26/9 - 2/10)</v>
       </c>
       <c r="H154" s="45">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="I154" s="47" t="s">
-        <v>451</v>
-      </c>
-      <c r="J154" s="44" t="s">
-        <v>168</v>
-      </c>
-      <c r="K154" s="44" t="s">
-        <v>169</v>
+        <v>199</v>
+      </c>
+      <c r="J154" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="K154" s="55" t="s">
+        <v>193</v>
       </c>
       <c r="L154" s="48" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="M154" s="49" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="155" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="43">
         <v>154</v>
       </c>
       <c r="B155" s="43" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C155" s="44" t="s">
         <v>116</v>
@@ -48744,7 +48801,7 @@
         <v>Inadequate or Improper Protective</v>
       </c>
       <c r="F155" s="45">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="G155" s="45" t="str">
         <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
@@ -48756,40 +48813,40 @@
         <v>W25 (26/9 - 2/10)</v>
       </c>
       <c r="H155" s="45">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="I155" s="47" t="s">
-        <v>217</v>
-      </c>
-      <c r="J155" s="44" t="s">
-        <v>168</v>
-      </c>
-      <c r="K155" s="44" t="s">
-        <v>169</v>
+        <v>230</v>
+      </c>
+      <c r="J155" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="K155" s="55" t="s">
+        <v>193</v>
       </c>
       <c r="L155" s="48" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="M155" s="49" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="156" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="43">
         <v>155</v>
       </c>
       <c r="B156" s="43" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="C156" s="44" t="s">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="D156" s="44" t="s">
         <v>70</v>
       </c>
       <c r="E156" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
-        <v>Safe Act</v>
+        <v>Safe Condition</v>
       </c>
       <c r="F156" s="45">
         <v>46297</v>
@@ -48807,37 +48864,37 @@
         <v>46297</v>
       </c>
       <c r="I156" s="47" t="s">
-        <v>456</v>
-      </c>
-      <c r="J156" s="44" t="s">
+        <v>237</v>
+      </c>
+      <c r="J156" s="55" t="s">
         <v>168</v>
       </c>
-      <c r="K156" s="44" t="s">
-        <v>169</v>
+      <c r="K156" s="55" t="s">
+        <v>175</v>
       </c>
       <c r="L156" s="48" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="M156" s="49" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="157" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="43">
         <v>156</v>
       </c>
       <c r="B157" s="43" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="C157" s="44" t="s">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="D157" s="44" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="E157" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
-        <v>Others - Hazardous Environmental Condition</v>
+        <v>Safe Condition</v>
       </c>
       <c r="F157" s="45">
         <v>46297</v>
@@ -48855,27 +48912,27 @@
         <v>46297</v>
       </c>
       <c r="I157" s="47" t="s">
-        <v>262</v>
-      </c>
-      <c r="J157" s="44" t="s">
-        <v>168</v>
-      </c>
-      <c r="K157" s="44" t="s">
-        <v>169</v>
+        <v>331</v>
+      </c>
+      <c r="J157" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="K157" s="55" t="s">
+        <v>193</v>
       </c>
       <c r="L157" s="48" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="M157" s="49" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="158" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="43">
         <v>157</v>
       </c>
       <c r="B158" s="43" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="C158" s="44" t="s">
         <v>77</v>
@@ -48903,37 +48960,37 @@
         <v>46297</v>
       </c>
       <c r="I158" s="47" t="s">
-        <v>237</v>
-      </c>
-      <c r="J158" s="44" t="s">
+        <v>451</v>
+      </c>
+      <c r="J158" s="55" t="s">
         <v>168</v>
       </c>
-      <c r="K158" s="44" t="s">
-        <v>175</v>
+      <c r="K158" s="55" t="s">
+        <v>169</v>
       </c>
       <c r="L158" s="48" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="M158" s="49" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="159" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="43">
         <v>158</v>
       </c>
       <c r="B159" s="43" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="C159" s="44" t="s">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="D159" s="44" t="s">
-        <v>70</v>
+        <v>429</v>
       </c>
       <c r="E159" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
-        <v>Safe Condition</v>
+        <v>Inadequate or Improper Protective</v>
       </c>
       <c r="F159" s="45">
         <v>46297</v>
@@ -48951,37 +49008,37 @@
         <v>46297</v>
       </c>
       <c r="I159" s="47" t="s">
-        <v>463</v>
-      </c>
-      <c r="J159" s="44" t="s">
+        <v>217</v>
+      </c>
+      <c r="J159" s="55" t="s">
         <v>168</v>
       </c>
-      <c r="K159" s="44" t="s">
+      <c r="K159" s="55" t="s">
         <v>169</v>
       </c>
       <c r="L159" s="48" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="M159" s="49" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="160" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="43">
         <v>159</v>
       </c>
       <c r="B160" s="43" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="C160" s="44" t="s">
-        <v>88</v>
+        <v>149</v>
       </c>
       <c r="D160" s="44" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="E160" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
-        <v>Inadequate Guards or Barriers</v>
+        <v>Safe Act</v>
       </c>
       <c r="F160" s="45">
         <v>46297</v>
@@ -48999,37 +49056,37 @@
         <v>46297</v>
       </c>
       <c r="I160" s="47" t="s">
-        <v>466</v>
-      </c>
-      <c r="J160" s="44" t="s">
-        <v>82</v>
-      </c>
-      <c r="K160" s="44" t="s">
-        <v>175</v>
+        <v>456</v>
+      </c>
+      <c r="J160" s="55" t="s">
+        <v>168</v>
+      </c>
+      <c r="K160" s="55" t="s">
+        <v>169</v>
       </c>
       <c r="L160" s="48" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="M160" s="49" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="161" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="43">
         <v>160</v>
       </c>
       <c r="B161" s="43" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="C161" s="44" t="s">
-        <v>88</v>
+        <v>142</v>
       </c>
       <c r="D161" s="44" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="E161" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
-        <v>Inadequate Warning System</v>
+        <v>Others - Hazardous Environmental Condition</v>
       </c>
       <c r="F161" s="45">
         <v>46297</v>
@@ -49047,37 +49104,37 @@
         <v>46297</v>
       </c>
       <c r="I161" s="47" t="s">
-        <v>469</v>
-      </c>
-      <c r="J161" s="44" t="s">
+        <v>262</v>
+      </c>
+      <c r="J161" s="55" t="s">
         <v>168</v>
       </c>
-      <c r="K161" s="44" t="s">
-        <v>175</v>
+      <c r="K161" s="55" t="s">
+        <v>169</v>
       </c>
       <c r="L161" s="48" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="M161" s="49" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="162" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="43">
         <v>161</v>
       </c>
       <c r="B162" s="43" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="C162" s="44" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D162" s="44" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="E162" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
-        <v>Others - Unsafe Condition</v>
+        <v>Safe Condition</v>
       </c>
       <c r="F162" s="45">
         <v>46297</v>
@@ -49092,40 +49149,40 @@
         <v>W25 (26/9 - 2/10)</v>
       </c>
       <c r="H162" s="45">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="I162" s="47" t="s">
-        <v>472</v>
-      </c>
-      <c r="J162" s="44" t="s">
+        <v>237</v>
+      </c>
+      <c r="J162" s="55" t="s">
         <v>168</v>
       </c>
-      <c r="K162" s="44" t="s">
-        <v>193</v>
+      <c r="K162" s="55" t="s">
+        <v>175</v>
       </c>
       <c r="L162" s="48" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="M162" s="49" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="163" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="43">
         <v>162</v>
       </c>
       <c r="B163" s="43" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="C163" s="44" t="s">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="D163" s="44" t="s">
         <v>70</v>
       </c>
       <c r="E163" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
-        <v>Safe Act</v>
+        <v>Safe Condition</v>
       </c>
       <c r="F163" s="45">
         <v>46297</v>
@@ -49143,37 +49200,37 @@
         <v>46297</v>
       </c>
       <c r="I163" s="47" t="s">
-        <v>475</v>
-      </c>
-      <c r="J163" s="44" t="s">
+        <v>463</v>
+      </c>
+      <c r="J163" s="55" t="s">
         <v>168</v>
       </c>
-      <c r="K163" s="44" t="s">
+      <c r="K163" s="55" t="s">
         <v>169</v>
       </c>
       <c r="L163" s="48" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="M163" s="49" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="164" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="43">
         <v>163</v>
       </c>
       <c r="B164" s="43" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="C164" s="44" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="D164" s="44" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="E164" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
-        <v>Suggestion for Improvement</v>
+        <v>Inadequate Guards or Barriers</v>
       </c>
       <c r="F164" s="45">
         <v>46297</v>
@@ -49188,40 +49245,40 @@
         <v>W25 (26/9 - 2/10)</v>
       </c>
       <c r="H164" s="45">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="I164" s="47" t="s">
-        <v>478</v>
-      </c>
-      <c r="J164" s="44" t="s">
+        <v>466</v>
+      </c>
+      <c r="J164" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="K164" s="44" t="s">
+      <c r="K164" s="55" t="s">
         <v>175</v>
       </c>
       <c r="L164" s="48" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="M164" s="49" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="165" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="43">
         <v>164</v>
       </c>
       <c r="B165" s="43" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="C165" s="44" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="D165" s="44" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="E165" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
-        <v>Safe Condition</v>
+        <v>Inadequate Warning System</v>
       </c>
       <c r="F165" s="45">
         <v>46297</v>
@@ -49239,37 +49296,37 @@
         <v>46297</v>
       </c>
       <c r="I165" s="47" t="s">
-        <v>481</v>
-      </c>
-      <c r="J165" s="44" t="s">
-        <v>82</v>
-      </c>
-      <c r="K165" s="44" t="s">
+        <v>469</v>
+      </c>
+      <c r="J165" s="55" t="s">
+        <v>168</v>
+      </c>
+      <c r="K165" s="55" t="s">
         <v>175</v>
       </c>
       <c r="L165" s="48" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="M165" s="49" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="166" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="43">
         <v>165</v>
       </c>
       <c r="B166" s="43" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="C166" s="44" t="s">
         <v>88</v>
       </c>
       <c r="D166" s="44" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="E166" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
-        <v>Inadequate Guards or Barriers</v>
+        <v>Others - Unsafe Condition</v>
       </c>
       <c r="F166" s="45">
         <v>46297</v>
@@ -49284,40 +49341,40 @@
         <v>W25 (26/9 - 2/10)</v>
       </c>
       <c r="H166" s="45">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="I166" s="47" t="s">
-        <v>478</v>
-      </c>
-      <c r="J166" s="44" t="s">
-        <v>82</v>
-      </c>
-      <c r="K166" s="44" t="s">
-        <v>175</v>
+        <v>472</v>
+      </c>
+      <c r="J166" s="55" t="s">
+        <v>168</v>
+      </c>
+      <c r="K166" s="55" t="s">
+        <v>193</v>
       </c>
       <c r="L166" s="48" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="M166" s="49" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="167" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="43">
         <v>166</v>
       </c>
       <c r="B167" s="43" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="C167" s="44" t="s">
-        <v>69</v>
+        <v>149</v>
       </c>
       <c r="D167" s="44" t="s">
         <v>70</v>
       </c>
       <c r="E167" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
-        <v>Suggestion for Improvement</v>
+        <v>Safe Act</v>
       </c>
       <c r="F167" s="45">
         <v>46297</v>
@@ -49335,37 +49392,37 @@
         <v>46297</v>
       </c>
       <c r="I167" s="47" t="s">
-        <v>199</v>
-      </c>
-      <c r="J167" s="44" t="s">
-        <v>82</v>
-      </c>
-      <c r="K167" s="44" t="s">
-        <v>193</v>
+        <v>475</v>
+      </c>
+      <c r="J167" s="55" t="s">
+        <v>168</v>
+      </c>
+      <c r="K167" s="55" t="s">
+        <v>169</v>
       </c>
       <c r="L167" s="48" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="M167" s="49" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="168" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="43">
         <v>167</v>
       </c>
       <c r="B168" s="43" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="C168" s="44" t="s">
-        <v>142</v>
+        <v>69</v>
       </c>
       <c r="D168" s="44" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="E168" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
-        <v>Others - Hazardous Environmental Condition</v>
+        <v>Suggestion for Improvement</v>
       </c>
       <c r="F168" s="45">
         <v>46297</v>
@@ -49380,40 +49437,40 @@
         <v>W25 (26/9 - 2/10)</v>
       </c>
       <c r="H168" s="45">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="I168" s="47" t="s">
-        <v>199</v>
-      </c>
-      <c r="J168" s="44" t="s">
+        <v>478</v>
+      </c>
+      <c r="J168" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="K168" s="44" t="s">
-        <v>193</v>
+      <c r="K168" s="55" t="s">
+        <v>175</v>
       </c>
       <c r="L168" s="48" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="M168" s="49" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="169" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="43">
         <v>168</v>
       </c>
       <c r="B169" s="43" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="C169" s="44" t="s">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="D169" s="44" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="E169" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
-        <v>Others - Hazardous Environmental Condition</v>
+        <v>Safe Condition</v>
       </c>
       <c r="F169" s="45">
         <v>46297</v>
@@ -49431,37 +49488,37 @@
         <v>46297</v>
       </c>
       <c r="I169" s="47" t="s">
-        <v>81</v>
-      </c>
-      <c r="J169" s="44" t="s">
+        <v>481</v>
+      </c>
+      <c r="J169" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="K169" s="44" t="s">
-        <v>73</v>
+      <c r="K169" s="55" t="s">
+        <v>175</v>
       </c>
       <c r="L169" s="48" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="M169" s="49" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="170" spans="1:13" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="43">
         <v>169</v>
       </c>
       <c r="B170" s="43" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="C170" s="44" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="D170" s="44" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="E170" s="44" t="str">
         <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
-        <v>Safe Condition</v>
+        <v>Inadequate Guards or Barriers</v>
       </c>
       <c r="F170" s="45">
         <v>46297</v>
@@ -49479,18 +49536,210 @@
         <v>46297</v>
       </c>
       <c r="I170" s="47" t="s">
+        <v>478</v>
+      </c>
+      <c r="J170" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="K170" s="55" t="s">
+        <v>175</v>
+      </c>
+      <c r="L170" s="48" t="s">
+        <v>484</v>
+      </c>
+      <c r="M170" s="49" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="56">
+        <v>170</v>
+      </c>
+      <c r="B171" s="57" t="s">
+        <v>485</v>
+      </c>
+      <c r="C171" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="D171" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="E171" s="58" t="str">
+        <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
+        <v>Suggestion for Improvement</v>
+      </c>
+      <c r="F171" s="52">
+        <v>46297</v>
+      </c>
+      <c r="G171" s="52" t="str">
+        <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
+_xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
+_xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
+_xlpm.E,_xlpm.S+6,
+"W"&amp;TEXT(_xlpm.W,"00")&amp;" ("&amp;TEXT(_xlpm.S,"d/m")&amp;" - "&amp;TEXT(_xlpm.E,"d/m")&amp;")"
+))</f>
+        <v>W25 (26/9 - 2/10)</v>
+      </c>
+      <c r="H171" s="52">
+        <v>46297</v>
+      </c>
+      <c r="I171" s="59" t="s">
+        <v>199</v>
+      </c>
+      <c r="J171" s="60" t="s">
+        <v>82</v>
+      </c>
+      <c r="K171" s="60" t="s">
+        <v>193</v>
+      </c>
+      <c r="L171" s="61" t="s">
+        <v>486</v>
+      </c>
+      <c r="M171" s="54" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="56">
+        <v>171</v>
+      </c>
+      <c r="B172" s="57" t="s">
+        <v>487</v>
+      </c>
+      <c r="C172" s="54" t="s">
+        <v>142</v>
+      </c>
+      <c r="D172" s="54" t="s">
+        <v>117</v>
+      </c>
+      <c r="E172" s="62" t="str">
+        <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
+        <v>Others - Hazardous Environmental Condition</v>
+      </c>
+      <c r="F172" s="52">
+        <v>46297</v>
+      </c>
+      <c r="G172" s="53" t="str">
+        <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
+_xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
+_xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
+_xlpm.E,_xlpm.S+6,
+"W"&amp;TEXT(_xlpm.W,"00")&amp;" ("&amp;TEXT(_xlpm.S,"d/m")&amp;" - "&amp;TEXT(_xlpm.E,"d/m")&amp;")"
+))</f>
+        <v>W25 (26/9 - 2/10)</v>
+      </c>
+      <c r="H172" s="52">
+        <v>46297</v>
+      </c>
+      <c r="I172" s="59" t="s">
+        <v>199</v>
+      </c>
+      <c r="J172" s="60" t="s">
+        <v>82</v>
+      </c>
+      <c r="K172" s="60" t="s">
+        <v>193</v>
+      </c>
+      <c r="L172" s="61" t="s">
+        <v>488</v>
+      </c>
+      <c r="M172" s="54" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="56">
+        <v>172</v>
+      </c>
+      <c r="B173" s="57" t="s">
+        <v>489</v>
+      </c>
+      <c r="C173" s="54" t="s">
+        <v>142</v>
+      </c>
+      <c r="D173" s="54" t="s">
+        <v>117</v>
+      </c>
+      <c r="E173" s="62" t="str">
+        <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
+        <v>Others - Hazardous Environmental Condition</v>
+      </c>
+      <c r="F173" s="52">
+        <v>46297</v>
+      </c>
+      <c r="G173" s="53" t="str">
+        <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
+_xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
+_xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
+_xlpm.E,_xlpm.S+6,
+"W"&amp;TEXT(_xlpm.W,"00")&amp;" ("&amp;TEXT(_xlpm.S,"d/m")&amp;" - "&amp;TEXT(_xlpm.E,"d/m")&amp;")"
+))</f>
+        <v>W25 (26/9 - 2/10)</v>
+      </c>
+      <c r="H173" s="52">
+        <v>46297</v>
+      </c>
+      <c r="I173" s="59" t="s">
+        <v>81</v>
+      </c>
+      <c r="J173" s="60" t="s">
+        <v>82</v>
+      </c>
+      <c r="K173" s="60" t="s">
+        <v>73</v>
+      </c>
+      <c r="L173" s="61" t="s">
+        <v>490</v>
+      </c>
+      <c r="M173" s="54" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="56">
+        <v>173</v>
+      </c>
+      <c r="B174" s="57" t="s">
+        <v>491</v>
+      </c>
+      <c r="C174" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="D174" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="E174" s="62" t="str">
+        <f>IF(Table3[[#This Row],[Hazard Type RAW]]="NA",Table3[[#This Row],[BSC Type]],IF(Table3[[#This Row],[Hazard Type RAW]]="Others","Others - "&amp;Table3[[#This Row],[BSC Type]],Table3[[#This Row],[Hazard Type RAW]]))</f>
+        <v>Safe Condition</v>
+      </c>
+      <c r="F174" s="52">
+        <v>46297</v>
+      </c>
+      <c r="G174" s="53" t="str">
+        <f>IF(Table3[[#This Row],[Date Reported]]&lt;DATE(2026,4,11),"0",_xlfn.LET(
+_xlpm.W,INT((Table3[[#This Row],[Date Reported]]-DATE(2026,4,11))/7)+1,
+_xlpm.S,DATE(2026,4,11)+(_xlpm.W-1)*7,
+_xlpm.E,_xlpm.S+6,
+"W"&amp;TEXT(_xlpm.W,"00")&amp;" ("&amp;TEXT(_xlpm.S,"d/m")&amp;" - "&amp;TEXT(_xlpm.E,"d/m")&amp;")"
+))</f>
+        <v>W25 (26/9 - 2/10)</v>
+      </c>
+      <c r="H174" s="52">
+        <v>46297</v>
+      </c>
+      <c r="I174" s="59" t="s">
         <v>492</v>
       </c>
-      <c r="J170" s="44" t="s">
+      <c r="J174" s="60" t="s">
         <v>168</v>
       </c>
-      <c r="K170" s="44" t="s">
+      <c r="K174" s="60" t="s">
         <v>169</v>
       </c>
-      <c r="L170" s="48" t="s">
+      <c r="L174" s="61" t="s">
         <v>493</v>
       </c>
-      <c r="M170" s="49" t="s">
+      <c r="M174" s="54" t="s">
         <v>75</v>
       </c>
     </row>
